--- a/research/traditional_assets/database/data/mauritius/mauritius_power.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_power.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07816376228889582</v>
+        <v>0.07808476664546246</v>
       </c>
       <c r="C2">
-        <v>182.2866624870861</v>
+        <v>180.8844227467461</v>
       </c>
       <c r="D2">
-        <v>182.2866624870861</v>
+        <v>182.4554227467461</v>
       </c>
       <c r="E2">
-        <v>-126.7</v>
+        <v>-125.129</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.571</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>26.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07902129999999999</v>
       </c>
       <c r="N2">
-        <v>26.5</v>
+        <v>26.4209787</v>
       </c>
       <c r="O2">
-        <v>3.975</v>
+        <v>3.963146805</v>
       </c>
       <c r="P2">
-        <v>22.525</v>
+        <v>22.457831895</v>
       </c>
       <c r="Q2">
-        <v>35.625</v>
+        <v>35.557831895</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07816376228889582</v>
+        <v>0.07844163297521461</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4493243643771281</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>335.3526201163484</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07808476664546246</v>
+        <v>0.07800577100202914</v>
       </c>
       <c r="C3">
-        <v>180.8844227467461</v>
+        <v>179.4824957711028</v>
       </c>
       <c r="D3">
-        <v>182.4554227467461</v>
+        <v>182.6244957711028</v>
       </c>
       <c r="E3">
-        <v>-125.129</v>
+        <v>-123.558</v>
       </c>
       <c r="F3">
-        <v>1.571</v>
+        <v>3.142</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1527,28 +1527,28 @@
         <v>26.5</v>
       </c>
       <c r="M3">
-        <v>0.07902129999999999</v>
+        <v>0.1580426</v>
       </c>
       <c r="N3">
-        <v>26.4209787</v>
+        <v>26.3419574</v>
       </c>
       <c r="O3">
-        <v>3.963146805</v>
+        <v>3.95129361</v>
       </c>
       <c r="P3">
-        <v>22.457831895</v>
+        <v>22.39066379</v>
       </c>
       <c r="Q3">
-        <v>35.557831895</v>
+        <v>35.49066379</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07844163297521461</v>
+        <v>0.07872517449186647</v>
       </c>
       <c r="T3">
-        <v>0.4493243643771281</v>
+        <v>0.4532274200802804</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>335.3526201163484</v>
+        <v>167.6763100581742</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07800577100202914</v>
+        <v>0.07792677535859578</v>
       </c>
       <c r="C4">
-        <v>179.4824957711028</v>
+        <v>178.0808824304368</v>
       </c>
       <c r="D4">
-        <v>182.6244957711028</v>
+        <v>182.7938824304368</v>
       </c>
       <c r="E4">
-        <v>-123.558</v>
+        <v>-121.987</v>
       </c>
       <c r="F4">
-        <v>3.142</v>
+        <v>4.713</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         <v>26.5</v>
       </c>
       <c r="M4">
-        <v>0.1580426</v>
+        <v>0.2370639</v>
       </c>
       <c r="N4">
-        <v>26.3419574</v>
+        <v>26.2629361</v>
       </c>
       <c r="O4">
-        <v>3.95129361</v>
+        <v>3.939440415</v>
       </c>
       <c r="P4">
-        <v>22.39066379</v>
+        <v>22.323495685</v>
       </c>
       <c r="Q4">
-        <v>35.49066379</v>
+        <v>35.423495685</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07872517449186647</v>
+        <v>0.07901456222535648</v>
       </c>
       <c r="T4">
-        <v>0.4532274200802804</v>
+        <v>0.4572109511587553</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>167.6763100581742</v>
+        <v>111.7842067054495</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07792677535859578</v>
+        <v>0.07784777971516244</v>
       </c>
       <c r="C5">
-        <v>178.0808824304368</v>
+        <v>176.6795835982599</v>
       </c>
       <c r="D5">
-        <v>182.7938824304368</v>
+        <v>182.9635835982599</v>
       </c>
       <c r="E5">
-        <v>-121.987</v>
+        <v>-120.416</v>
       </c>
       <c r="F5">
-        <v>4.713</v>
+        <v>6.284</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1691,28 +1691,28 @@
         <v>26.5</v>
       </c>
       <c r="M5">
-        <v>0.2370639</v>
+        <v>0.3160852</v>
       </c>
       <c r="N5">
-        <v>26.2629361</v>
+        <v>26.1839148</v>
       </c>
       <c r="O5">
-        <v>3.939440415</v>
+        <v>3.92758722</v>
       </c>
       <c r="P5">
-        <v>22.323495685</v>
+        <v>22.25632758</v>
       </c>
       <c r="Q5">
-        <v>35.423495685</v>
+        <v>35.35632758</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07901456222535648</v>
+        <v>0.07930997886996088</v>
       </c>
       <c r="T5">
-        <v>0.4572109511587553</v>
+        <v>0.4612774724680319</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>111.7842067054495</v>
+        <v>83.8381550290871</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07784777971516244</v>
+        <v>0.07776878407172909</v>
       </c>
       <c r="C6">
-        <v>176.6795835982599</v>
+        <v>175.2786001513312</v>
       </c>
       <c r="D6">
-        <v>182.9635835982599</v>
+        <v>183.1336001513312</v>
       </c>
       <c r="E6">
-        <v>-120.416</v>
+        <v>-118.845</v>
       </c>
       <c r="F6">
-        <v>6.284</v>
+        <v>7.855</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1773,28 +1773,28 @@
         <v>26.5</v>
       </c>
       <c r="M6">
-        <v>0.3160852</v>
+        <v>0.3951065</v>
       </c>
       <c r="N6">
-        <v>26.1839148</v>
+        <v>26.1048935</v>
       </c>
       <c r="O6">
-        <v>3.92758722</v>
+        <v>3.915734025</v>
       </c>
       <c r="P6">
-        <v>22.25632758</v>
+        <v>22.189159475</v>
       </c>
       <c r="Q6">
-        <v>35.35632758</v>
+        <v>35.289159475</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07930997886996088</v>
+        <v>0.07961161481234642</v>
       </c>
       <c r="T6">
-        <v>0.4612774724680319</v>
+        <v>0.4654296047522407</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>83.8381550290871</v>
+        <v>67.07052402326967</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07776878407172909</v>
+        <v>0.07768978842829577</v>
       </c>
       <c r="C7">
-        <v>175.2786001513312</v>
+        <v>173.8779329696714</v>
       </c>
       <c r="D7">
-        <v>183.1336001513312</v>
+        <v>183.3039329696714</v>
       </c>
       <c r="E7">
-        <v>-118.845</v>
+        <v>-117.274</v>
       </c>
       <c r="F7">
-        <v>7.855</v>
+        <v>9.426</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1855,28 +1855,28 @@
         <v>26.5</v>
       </c>
       <c r="M7">
-        <v>0.3951065</v>
+        <v>0.4741278</v>
       </c>
       <c r="N7">
-        <v>26.1048935</v>
+        <v>26.0258722</v>
       </c>
       <c r="O7">
-        <v>3.915734025</v>
+        <v>3.903880829999999</v>
       </c>
       <c r="P7">
-        <v>22.189159475</v>
+        <v>22.12199137</v>
       </c>
       <c r="Q7">
-        <v>35.289159475</v>
+        <v>35.22199137</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07961161481234642</v>
+        <v>0.07991966854074017</v>
       </c>
       <c r="T7">
-        <v>0.4654296047522407</v>
+        <v>0.4696700802765388</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>67.07052402326967</v>
+        <v>55.89210335272472</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07768978842829577</v>
+        <v>0.07761079278486244</v>
       </c>
       <c r="C8">
-        <v>173.8779329696714</v>
+        <v>172.4775829365784</v>
       </c>
       <c r="D8">
-        <v>183.3039329696714</v>
+        <v>183.4745829365783</v>
       </c>
       <c r="E8">
-        <v>-117.274</v>
+        <v>-115.703</v>
       </c>
       <c r="F8">
-        <v>9.426</v>
+        <v>10.997</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1937,28 +1937,28 @@
         <v>26.5</v>
       </c>
       <c r="M8">
-        <v>0.4741278</v>
+        <v>0.5531490999999998</v>
       </c>
       <c r="N8">
-        <v>26.0258722</v>
+        <v>25.9468509</v>
       </c>
       <c r="O8">
-        <v>3.903880829999999</v>
+        <v>3.892027635</v>
       </c>
       <c r="P8">
-        <v>22.12199137</v>
+        <v>22.054823265</v>
       </c>
       <c r="Q8">
-        <v>35.22199137</v>
+        <v>35.154823265</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07991966854074017</v>
+        <v>0.08023434708049723</v>
       </c>
       <c r="T8">
-        <v>0.4696700802765388</v>
+        <v>0.4740017488228651</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>55.89210335272472</v>
+        <v>47.90751715947835</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07761079278486242</v>
+        <v>0.07753179714142908</v>
       </c>
       <c r="C9">
-        <v>172.4775829365784</v>
+        <v>171.0775509386423</v>
       </c>
       <c r="D9">
-        <v>183.4745829365784</v>
+        <v>183.6455509386423</v>
       </c>
       <c r="E9">
-        <v>-115.703</v>
+        <v>-114.132</v>
       </c>
       <c r="F9">
-        <v>10.997</v>
+        <v>12.568</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2019,28 +2019,28 @@
         <v>26.5</v>
       </c>
       <c r="M9">
-        <v>0.5531490999999999</v>
+        <v>0.6321703999999999</v>
       </c>
       <c r="N9">
-        <v>25.9468509</v>
+        <v>25.8678296</v>
       </c>
       <c r="O9">
-        <v>3.892027635</v>
+        <v>3.88017444</v>
       </c>
       <c r="P9">
-        <v>22.054823265</v>
+        <v>21.98765516</v>
       </c>
       <c r="Q9">
-        <v>35.154823265</v>
+        <v>35.08765516</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08023434708049723</v>
+        <v>0.08055586645807508</v>
       </c>
       <c r="T9">
-        <v>0.4740017488228651</v>
+        <v>0.47842758407672</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>47.90751715947835</v>
+        <v>41.91907751454355</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07753179714142908</v>
+        <v>0.07745280149799573</v>
       </c>
       <c r="C10">
-        <v>171.0775509386423</v>
+        <v>169.6778378657612</v>
       </c>
       <c r="D10">
-        <v>183.6455509386423</v>
+        <v>183.8168378657612</v>
       </c>
       <c r="E10">
-        <v>-114.132</v>
+        <v>-112.561</v>
       </c>
       <c r="F10">
-        <v>12.568</v>
+        <v>14.139</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2101,28 +2101,28 @@
         <v>26.5</v>
       </c>
       <c r="M10">
-        <v>0.6321703999999999</v>
+        <v>0.7111917</v>
       </c>
       <c r="N10">
-        <v>25.8678296</v>
+        <v>25.7888083</v>
       </c>
       <c r="O10">
-        <v>3.88017444</v>
+        <v>3.868321245</v>
       </c>
       <c r="P10">
-        <v>21.98765516</v>
+        <v>21.920487055</v>
       </c>
       <c r="Q10">
-        <v>35.08765516</v>
+        <v>35.020487055</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08055586645807508</v>
+        <v>0.0808844521955997</v>
       </c>
       <c r="T10">
-        <v>0.47842758407672</v>
+        <v>0.4829506904350553</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.91907751454355</v>
+        <v>37.26140223514982</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07745280149799573</v>
+        <v>0.0773738058545624</v>
       </c>
       <c r="C11">
-        <v>169.6778378657612</v>
+        <v>168.2784446111561</v>
       </c>
       <c r="D11">
-        <v>183.8168378657612</v>
+        <v>183.9884446111561</v>
       </c>
       <c r="E11">
-        <v>-112.561</v>
+        <v>-110.99</v>
       </c>
       <c r="F11">
-        <v>14.139</v>
+        <v>15.71</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2183,28 +2183,28 @@
         <v>26.5</v>
       </c>
       <c r="M11">
-        <v>0.7111917</v>
+        <v>0.7902129999999998</v>
       </c>
       <c r="N11">
-        <v>25.7888083</v>
+        <v>25.709787</v>
       </c>
       <c r="O11">
-        <v>3.868321245</v>
+        <v>3.85646805</v>
       </c>
       <c r="P11">
-        <v>21.920487055</v>
+        <v>21.85331895</v>
       </c>
       <c r="Q11">
-        <v>35.020487055</v>
+        <v>34.95331895</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0808844521955997</v>
+        <v>0.08122033983840266</v>
       </c>
       <c r="T11">
-        <v>0.4829506904350553</v>
+        <v>0.4875743102680204</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.26140223514982</v>
+        <v>33.53526201163484</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0773738058545624</v>
+        <v>0.07729481021112905</v>
       </c>
       <c r="C12">
-        <v>168.2784446111561</v>
+        <v>166.8793720713867</v>
       </c>
       <c r="D12">
-        <v>183.9884446111561</v>
+        <v>184.1603720713867</v>
       </c>
       <c r="E12">
-        <v>-110.99</v>
+        <v>-109.419</v>
       </c>
       <c r="F12">
-        <v>15.71</v>
+        <v>17.281</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2265,28 +2265,28 @@
         <v>26.5</v>
       </c>
       <c r="M12">
-        <v>0.7902130000000001</v>
+        <v>0.8692342999999999</v>
       </c>
       <c r="N12">
-        <v>25.709787</v>
+        <v>25.6307657</v>
       </c>
       <c r="O12">
-        <v>3.85646805</v>
+        <v>3.844614855</v>
       </c>
       <c r="P12">
-        <v>21.85331895</v>
+        <v>21.786150845</v>
       </c>
       <c r="Q12">
-        <v>34.95331895</v>
+        <v>34.886150845</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08122033983840266</v>
+        <v>0.08156377551812252</v>
       </c>
       <c r="T12">
-        <v>0.4875743102680204</v>
+        <v>0.4923018316702655</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>33.53526201163483</v>
+        <v>30.48660182875895</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07729481021112905</v>
+        <v>0.0772158145676957</v>
       </c>
       <c r="C13">
-        <v>166.8793720713867</v>
+        <v>165.480621146367</v>
       </c>
       <c r="D13">
-        <v>184.1603720713867</v>
+        <v>184.332621146367</v>
       </c>
       <c r="E13">
-        <v>-109.419</v>
+        <v>-107.848</v>
       </c>
       <c r="F13">
-        <v>17.281</v>
+        <v>18.852</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2347,28 +2347,28 @@
         <v>26.5</v>
       </c>
       <c r="M13">
-        <v>0.8692342999999999</v>
+        <v>0.9482556</v>
       </c>
       <c r="N13">
-        <v>25.6307657</v>
+        <v>25.5517444</v>
       </c>
       <c r="O13">
-        <v>3.844614855</v>
+        <v>3.83276166</v>
       </c>
       <c r="P13">
-        <v>21.786150845</v>
+        <v>21.71898274</v>
       </c>
       <c r="Q13">
-        <v>34.886150845</v>
+        <v>34.81898274</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08156377551812252</v>
+        <v>0.08191501655419967</v>
       </c>
       <c r="T13">
-        <v>0.4923018316702655</v>
+        <v>0.4971367967407434</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.48660182875895</v>
+        <v>27.94605167636237</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0772158145676957</v>
+        <v>0.07713681892426236</v>
       </c>
       <c r="C14">
-        <v>165.480621146367</v>
+        <v>164.0821927393811</v>
       </c>
       <c r="D14">
-        <v>184.332621146367</v>
+        <v>184.5051927393811</v>
       </c>
       <c r="E14">
-        <v>-107.848</v>
+        <v>-106.277</v>
       </c>
       <c r="F14">
-        <v>18.852</v>
+        <v>20.423</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2429,28 +2429,28 @@
         <v>26.5</v>
       </c>
       <c r="M14">
-        <v>0.9482556</v>
+        <v>1.0272769</v>
       </c>
       <c r="N14">
-        <v>25.5517444</v>
+        <v>25.4727231</v>
       </c>
       <c r="O14">
-        <v>3.83276166</v>
+        <v>3.820908465</v>
       </c>
       <c r="P14">
-        <v>21.71898274</v>
+        <v>21.651814635</v>
       </c>
       <c r="Q14">
-        <v>34.81898274</v>
+        <v>34.751814635</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08191501655419967</v>
+        <v>0.08227433209685328</v>
       </c>
       <c r="T14">
-        <v>0.4971367967407434</v>
+        <v>0.5020829104335311</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.94605167636237</v>
+        <v>25.79635539356526</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07713681892426236</v>
+        <v>0.077057823280829</v>
       </c>
       <c r="C15">
-        <v>164.0821927393811</v>
+        <v>162.6840877570988</v>
       </c>
       <c r="D15">
-        <v>184.5051927393811</v>
+        <v>184.6780877570988</v>
       </c>
       <c r="E15">
-        <v>-106.277</v>
+        <v>-104.706</v>
       </c>
       <c r="F15">
-        <v>20.423</v>
+        <v>21.994</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2511,28 +2511,28 @@
         <v>26.5</v>
       </c>
       <c r="M15">
-        <v>1.0272769</v>
+        <v>1.1062982</v>
       </c>
       <c r="N15">
-        <v>25.4727231</v>
+        <v>25.3937018</v>
       </c>
       <c r="O15">
-        <v>3.820908465</v>
+        <v>3.80905527</v>
       </c>
       <c r="P15">
-        <v>21.651814635</v>
+        <v>21.58464653</v>
       </c>
       <c r="Q15">
-        <v>34.751814635</v>
+        <v>34.68464653</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08227433209685328</v>
+        <v>0.08264200381491744</v>
       </c>
       <c r="T15">
-        <v>0.5020829104335311</v>
+        <v>0.5071440500261511</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.79635539356526</v>
+        <v>23.95375857973917</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.077057823280829</v>
+        <v>0.07697882763739565</v>
       </c>
       <c r="C16">
-        <v>162.6840877570988</v>
+        <v>161.2863071095915</v>
       </c>
       <c r="D16">
-        <v>184.6780877570988</v>
+        <v>184.8513071095915</v>
       </c>
       <c r="E16">
-        <v>-104.706</v>
+        <v>-103.135</v>
       </c>
       <c r="F16">
-        <v>21.994</v>
+        <v>23.565</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2593,28 +2593,28 @@
         <v>26.5</v>
       </c>
       <c r="M16">
-        <v>1.1062982</v>
+        <v>1.1853195</v>
       </c>
       <c r="N16">
-        <v>25.3937018</v>
+        <v>25.3146805</v>
       </c>
       <c r="O16">
-        <v>3.80905527</v>
+        <v>3.797202075</v>
       </c>
       <c r="P16">
-        <v>21.58464653</v>
+        <v>21.517478425</v>
       </c>
       <c r="Q16">
-        <v>34.68464653</v>
+        <v>34.617478425</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08264200381491744</v>
+        <v>0.08301832663223019</v>
       </c>
       <c r="T16">
-        <v>0.5071440500261511</v>
+        <v>0.5123242752562447</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.95375857973917</v>
+        <v>22.35684134108989</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07697882763739565</v>
+        <v>0.07689983199396232</v>
       </c>
       <c r="C17">
-        <v>161.2863071095915</v>
+        <v>159.8888517103481</v>
       </c>
       <c r="D17">
-        <v>184.8513071095915</v>
+        <v>185.0248517103481</v>
       </c>
       <c r="E17">
-        <v>-103.135</v>
+        <v>-101.564</v>
       </c>
       <c r="F17">
-        <v>23.565</v>
+        <v>25.136</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2675,28 +2675,28 @@
         <v>26.5</v>
       </c>
       <c r="M17">
-        <v>1.1853195</v>
+        <v>1.2643408</v>
       </c>
       <c r="N17">
-        <v>25.3146805</v>
+        <v>25.2356592</v>
       </c>
       <c r="O17">
-        <v>3.797202075</v>
+        <v>3.78534888</v>
       </c>
       <c r="P17">
-        <v>21.517478425</v>
+        <v>21.45031032</v>
       </c>
       <c r="Q17">
-        <v>34.617478425</v>
+        <v>34.55031032</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08301832663223019</v>
+        <v>0.08340360951662182</v>
       </c>
       <c r="T17">
-        <v>0.5123242752562447</v>
+        <v>0.5176278391822928</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.3568413410899</v>
+        <v>20.95953875727178</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07689983199396232</v>
+        <v>0.07682083635052897</v>
       </c>
       <c r="C18">
-        <v>159.8888517103481</v>
+        <v>158.4917224762916</v>
       </c>
       <c r="D18">
-        <v>185.0248517103481</v>
+        <v>185.1987224762916</v>
       </c>
       <c r="E18">
-        <v>-101.564</v>
+        <v>-99.99299999999999</v>
       </c>
       <c r="F18">
-        <v>25.136</v>
+        <v>26.707</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>26.5</v>
       </c>
       <c r="M18">
-        <v>1.2643408</v>
+        <v>1.3433621</v>
       </c>
       <c r="N18">
-        <v>25.2356592</v>
+        <v>25.1566379</v>
       </c>
       <c r="O18">
-        <v>3.78534888</v>
+        <v>3.773495685</v>
       </c>
       <c r="P18">
-        <v>21.45031032</v>
+        <v>21.383142215</v>
       </c>
       <c r="Q18">
-        <v>34.55031032</v>
+        <v>34.483142215</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08340360951662182</v>
+        <v>0.08379817632593853</v>
       </c>
       <c r="T18">
-        <v>0.5176278391822928</v>
+        <v>0.5230591998294505</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.95953875727178</v>
+        <v>19.72662471272637</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07682083635052897</v>
+        <v>0.07674184070709564</v>
       </c>
       <c r="C19">
-        <v>158.4917224762916</v>
+        <v>157.0949203277943</v>
       </c>
       <c r="D19">
-        <v>185.1987224762916</v>
+        <v>185.3729203277943</v>
       </c>
       <c r="E19">
-        <v>-99.99299999999999</v>
+        <v>-98.422</v>
       </c>
       <c r="F19">
-        <v>26.707</v>
+        <v>28.278</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2839,28 +2839,28 @@
         <v>26.5</v>
       </c>
       <c r="M19">
-        <v>1.3433621</v>
+        <v>1.4223834</v>
       </c>
       <c r="N19">
-        <v>25.1566379</v>
+        <v>25.0776166</v>
       </c>
       <c r="O19">
-        <v>3.773495685</v>
+        <v>3.76164249</v>
       </c>
       <c r="P19">
-        <v>21.383142215</v>
+        <v>21.31597411</v>
       </c>
       <c r="Q19">
-        <v>34.483142215</v>
+        <v>34.41597411</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08379817632593853</v>
+        <v>0.08420236671597028</v>
       </c>
       <c r="T19">
-        <v>0.5230591998294505</v>
+        <v>0.5286230326875144</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.72662471272637</v>
+        <v>18.63070111757491</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07674184070709564</v>
+        <v>0.0766628450636623</v>
       </c>
       <c r="C20">
-        <v>157.0949203277943</v>
+        <v>155.6984461886951</v>
       </c>
       <c r="D20">
-        <v>185.3729203277943</v>
+        <v>185.5474461886951</v>
       </c>
       <c r="E20">
-        <v>-98.422</v>
+        <v>-96.851</v>
       </c>
       <c r="F20">
-        <v>28.278</v>
+        <v>29.849</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2921,28 +2921,28 @@
         <v>26.5</v>
       </c>
       <c r="M20">
-        <v>1.4223834</v>
+        <v>1.5014047</v>
       </c>
       <c r="N20">
-        <v>25.0776166</v>
+        <v>24.9985953</v>
       </c>
       <c r="O20">
-        <v>3.76164249</v>
+        <v>3.749789295</v>
       </c>
       <c r="P20">
-        <v>21.31597411</v>
+        <v>21.248806005</v>
       </c>
       <c r="Q20">
-        <v>34.41597411</v>
+        <v>34.348806005</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08420236671597028</v>
+        <v>0.08461653711563247</v>
       </c>
       <c r="T20">
-        <v>0.5286230326875144</v>
+        <v>0.5343242441346664</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.63070111757491</v>
+        <v>17.65013790086044</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0766628450636623</v>
+        <v>0.07658384942022894</v>
       </c>
       <c r="C21">
-        <v>155.6984461886951</v>
+        <v>154.3023009863149</v>
       </c>
       <c r="D21">
-        <v>185.5474461886951</v>
+        <v>185.722300986315</v>
       </c>
       <c r="E21">
-        <v>-96.851</v>
+        <v>-95.28</v>
       </c>
       <c r="F21">
-        <v>29.849</v>
+        <v>31.42</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3003,28 +3003,28 @@
         <v>26.5</v>
       </c>
       <c r="M21">
-        <v>1.5014047</v>
+        <v>1.580426</v>
       </c>
       <c r="N21">
-        <v>24.9985953</v>
+        <v>24.919574</v>
       </c>
       <c r="O21">
-        <v>3.749789295</v>
+        <v>3.7379361</v>
       </c>
       <c r="P21">
-        <v>21.248806005</v>
+        <v>21.1816379</v>
       </c>
       <c r="Q21">
-        <v>34.348806005</v>
+        <v>34.2816379</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08461653711563247</v>
+        <v>0.08504106177528617</v>
       </c>
       <c r="T21">
-        <v>0.5343242441346664</v>
+        <v>0.5401679858679971</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.65013790086044</v>
+        <v>16.76763100581742</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07658384942022894</v>
+        <v>0.07650485377679561</v>
       </c>
       <c r="C22">
-        <v>154.3023009863149</v>
+        <v>152.9064856514736</v>
       </c>
       <c r="D22">
-        <v>185.722300986315</v>
+        <v>185.8974856514737</v>
       </c>
       <c r="E22">
-        <v>-95.28</v>
+        <v>-93.709</v>
       </c>
       <c r="F22">
-        <v>31.42</v>
+        <v>32.991</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3085,28 +3085,28 @@
         <v>26.5</v>
       </c>
       <c r="M22">
-        <v>1.580426</v>
+        <v>1.6594473</v>
       </c>
       <c r="N22">
-        <v>24.919574</v>
+        <v>24.8405527</v>
       </c>
       <c r="O22">
-        <v>3.7379361</v>
+        <v>3.726082905</v>
       </c>
       <c r="P22">
-        <v>21.1816379</v>
+        <v>21.114469795</v>
       </c>
       <c r="Q22">
-        <v>34.2816379</v>
+        <v>34.214469795</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08504106177528617</v>
+        <v>0.08547633389467799</v>
       </c>
       <c r="T22">
-        <v>0.5401679858679971</v>
+        <v>0.5461596704300199</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.76763100581742</v>
+        <v>15.96917238649278</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07650485377679561</v>
+        <v>0.07642585813336226</v>
       </c>
       <c r="C23">
-        <v>152.9064856514736</v>
+        <v>151.5110011185065</v>
       </c>
       <c r="D23">
-        <v>185.8974856514737</v>
+        <v>186.0730011185065</v>
       </c>
       <c r="E23">
-        <v>-93.709</v>
+        <v>-92.13800000000001</v>
       </c>
       <c r="F23">
-        <v>32.991</v>
+        <v>34.562</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3167,28 +3167,28 @@
         <v>26.5</v>
       </c>
       <c r="M23">
-        <v>1.6594473</v>
+        <v>1.7384686</v>
       </c>
       <c r="N23">
-        <v>24.8405527</v>
+        <v>24.7615314</v>
       </c>
       <c r="O23">
-        <v>3.726082905</v>
+        <v>3.71422971</v>
       </c>
       <c r="P23">
-        <v>21.114469795</v>
+        <v>21.04730169</v>
       </c>
       <c r="Q23">
-        <v>34.214469795</v>
+        <v>34.14730169</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08547633389467799</v>
+        <v>0.08592276683764392</v>
       </c>
       <c r="T23">
-        <v>0.5461596704300198</v>
+        <v>0.5523049879295303</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.96917238649278</v>
+        <v>15.24330091437947</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07642585813336226</v>
+        <v>0.07634686248992892</v>
       </c>
       <c r="C24">
-        <v>151.5110011185065</v>
+        <v>150.1158483252806</v>
       </c>
       <c r="D24">
-        <v>186.0730011185065</v>
+        <v>186.2488483252806</v>
       </c>
       <c r="E24">
-        <v>-92.13800000000001</v>
+        <v>-90.56700000000001</v>
       </c>
       <c r="F24">
-        <v>34.562</v>
+        <v>36.133</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3249,28 +3249,28 @@
         <v>26.5</v>
       </c>
       <c r="M24">
-        <v>1.7384686</v>
+        <v>1.8174899</v>
       </c>
       <c r="N24">
-        <v>24.7615314</v>
+        <v>24.6825101</v>
       </c>
       <c r="O24">
-        <v>3.71422971</v>
+        <v>3.702376515</v>
       </c>
       <c r="P24">
-        <v>21.04730169</v>
+        <v>20.980133585</v>
       </c>
       <c r="Q24">
-        <v>34.14730169</v>
+        <v>34.080133585</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08592276683764392</v>
+        <v>0.08638079544146612</v>
       </c>
       <c r="T24">
-        <v>0.5523049879295303</v>
+        <v>0.5586099240653916</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.24330091437947</v>
+        <v>14.5805487007108</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07634686248992892</v>
+        <v>0.07626786684649557</v>
       </c>
       <c r="C25">
-        <v>150.1158483252806</v>
+        <v>148.7210282132118</v>
       </c>
       <c r="D25">
-        <v>186.2488483252806</v>
+        <v>186.4250282132118</v>
       </c>
       <c r="E25">
-        <v>-90.56700000000001</v>
+        <v>-88.99600000000001</v>
       </c>
       <c r="F25">
-        <v>36.133</v>
+        <v>37.704</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3331,28 +3331,28 @@
         <v>26.5</v>
       </c>
       <c r="M25">
-        <v>1.8174899</v>
+        <v>1.8965112</v>
       </c>
       <c r="N25">
-        <v>24.6825101</v>
+        <v>24.6034888</v>
       </c>
       <c r="O25">
-        <v>3.702376515</v>
+        <v>3.69052332</v>
       </c>
       <c r="P25">
-        <v>20.980133585</v>
+        <v>20.91296548</v>
       </c>
       <c r="Q25">
-        <v>34.080133585</v>
+        <v>34.01296548</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08638079544146612</v>
+        <v>0.08685087742959943</v>
       </c>
       <c r="T25">
-        <v>0.5586099240653916</v>
+        <v>0.5650807795732493</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.5805487007108</v>
+        <v>13.97302583818118</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07626786684649557</v>
+        <v>0.07618887120306223</v>
       </c>
       <c r="C26">
-        <v>148.7210282132118</v>
+        <v>147.3265417272813</v>
       </c>
       <c r="D26">
-        <v>186.4250282132118</v>
+        <v>186.6015417272813</v>
       </c>
       <c r="E26">
-        <v>-88.99600000000001</v>
+        <v>-87.42500000000001</v>
       </c>
       <c r="F26">
-        <v>37.704</v>
+        <v>39.275</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3413,28 +3413,28 @@
         <v>26.5</v>
       </c>
       <c r="M26">
-        <v>1.8965112</v>
+        <v>1.9755325</v>
       </c>
       <c r="N26">
-        <v>24.6034888</v>
+        <v>24.5244675</v>
       </c>
       <c r="O26">
-        <v>3.69052332</v>
+        <v>3.678670125</v>
       </c>
       <c r="P26">
-        <v>20.91296548</v>
+        <v>20.845797375</v>
       </c>
       <c r="Q26">
-        <v>34.01296548</v>
+        <v>33.945797375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08685087742959943</v>
+        <v>0.08733349493741629</v>
       </c>
       <c r="T26">
-        <v>0.5650807795732493</v>
+        <v>0.5717241912279832</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.97302583818118</v>
+        <v>13.41410480465394</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07618887120306223</v>
+        <v>0.07610987555962888</v>
       </c>
       <c r="C27">
-        <v>147.3265417272813</v>
+        <v>145.9323898160528</v>
       </c>
       <c r="D27">
-        <v>186.6015417272813</v>
+        <v>186.7783898160528</v>
       </c>
       <c r="E27">
-        <v>-87.42500000000001</v>
+        <v>-85.85400000000001</v>
       </c>
       <c r="F27">
-        <v>39.275</v>
+        <v>40.846</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3495,28 +3495,28 @@
         <v>26.5</v>
       </c>
       <c r="M27">
-        <v>1.9755325</v>
+        <v>2.0545538</v>
       </c>
       <c r="N27">
-        <v>24.5244675</v>
+        <v>24.4454462</v>
       </c>
       <c r="O27">
-        <v>3.678670125</v>
+        <v>3.66681693</v>
       </c>
       <c r="P27">
-        <v>20.845797375</v>
+        <v>20.77862927</v>
       </c>
       <c r="Q27">
-        <v>33.945797375</v>
+        <v>33.87862927</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08733349493741629</v>
+        <v>0.08782915616166065</v>
       </c>
       <c r="T27">
-        <v>0.5717241912279832</v>
+        <v>0.5785471545490612</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.41410480465394</v>
+        <v>12.89817769678263</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07610987555962888</v>
+        <v>0.07637512991619554</v>
       </c>
       <c r="C28">
-        <v>145.9323898160528</v>
+        <v>143.7688858208477</v>
       </c>
       <c r="D28">
-        <v>186.7783898160528</v>
+        <v>186.1858858208477</v>
       </c>
       <c r="E28">
-        <v>-85.85400000000001</v>
+        <v>-84.283</v>
       </c>
       <c r="F28">
-        <v>40.846</v>
+        <v>42.417</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3577,45 +3577,45 @@
         <v>26.5</v>
       </c>
       <c r="M28">
-        <v>2.0545538</v>
+        <v>2.1972006</v>
       </c>
       <c r="N28">
-        <v>24.4454462</v>
+        <v>24.3027994</v>
       </c>
       <c r="O28">
-        <v>3.66681693</v>
+        <v>3.64541991</v>
       </c>
       <c r="P28">
-        <v>20.77862927</v>
+        <v>20.65737949</v>
       </c>
       <c r="Q28">
-        <v>33.87862927</v>
+        <v>33.75737949</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08782915616166065</v>
+        <v>0.08833839714547334</v>
       </c>
       <c r="T28">
-        <v>0.5785471545490612</v>
+        <v>0.5855570483720868</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.15</v>
       </c>
       <c r="W28">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>12.89817769678263</v>
+        <v>12.06080136697578</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07637512991619554</v>
+        <v>0.07630888427276221</v>
       </c>
       <c r="C29">
-        <v>143.7688858208477</v>
+        <v>142.3455075922789</v>
       </c>
       <c r="D29">
-        <v>186.1858858208477</v>
+        <v>186.3335075922789</v>
       </c>
       <c r="E29">
-        <v>-84.283</v>
+        <v>-82.712</v>
       </c>
       <c r="F29">
-        <v>42.417</v>
+        <v>43.988</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3659,28 +3659,28 @@
         <v>26.5</v>
       </c>
       <c r="M29">
-        <v>2.1972006</v>
+        <v>2.2785784</v>
       </c>
       <c r="N29">
-        <v>24.3027994</v>
+        <v>24.2214216</v>
       </c>
       <c r="O29">
-        <v>3.64541991</v>
+        <v>3.63321324</v>
       </c>
       <c r="P29">
-        <v>20.65737949</v>
+        <v>20.58820836</v>
       </c>
       <c r="Q29">
-        <v>33.75737949</v>
+        <v>33.68820836</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08833839714547334</v>
+        <v>0.08886178371216973</v>
       </c>
       <c r="T29">
-        <v>0.5855570483720868</v>
+        <v>0.592761661467974</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.06080136697578</v>
+        <v>11.63005846101236</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07630888427276221</v>
+        <v>0.07624263862932887</v>
       </c>
       <c r="C30">
-        <v>142.3455075922789</v>
+        <v>140.9223636401105</v>
       </c>
       <c r="D30">
-        <v>186.3335075922789</v>
+        <v>186.4813636401105</v>
       </c>
       <c r="E30">
-        <v>-82.712</v>
+        <v>-81.14099999999999</v>
       </c>
       <c r="F30">
-        <v>43.988</v>
+        <v>45.559</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3741,28 +3741,28 @@
         <v>26.5</v>
       </c>
       <c r="M30">
-        <v>2.2785784</v>
+        <v>2.3599562</v>
       </c>
       <c r="N30">
-        <v>24.2214216</v>
+        <v>24.1400438</v>
       </c>
       <c r="O30">
-        <v>3.63321324</v>
+        <v>3.62100657</v>
       </c>
       <c r="P30">
-        <v>20.58820836</v>
+        <v>20.51903723</v>
       </c>
       <c r="Q30">
-        <v>33.68820836</v>
+        <v>33.61903723</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08886178371216973</v>
+        <v>0.08939991356243501</v>
       </c>
       <c r="T30">
-        <v>0.592761661467974</v>
+        <v>0.6001692214116328</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.63005846101236</v>
+        <v>11.22902196235676</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07624263862932885</v>
+        <v>0.07617639298589551</v>
       </c>
       <c r="C31">
-        <v>140.9223636401105</v>
+        <v>139.4994545224816</v>
       </c>
       <c r="D31">
-        <v>186.4813636401105</v>
+        <v>186.6294545224816</v>
       </c>
       <c r="E31">
-        <v>-81.14100000000001</v>
+        <v>-79.57000000000001</v>
       </c>
       <c r="F31">
-        <v>45.559</v>
+        <v>47.13</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3823,28 +3823,28 @@
         <v>26.5</v>
       </c>
       <c r="M31">
-        <v>2.3599562</v>
+        <v>2.441334</v>
       </c>
       <c r="N31">
-        <v>24.1400438</v>
+        <v>24.058666</v>
       </c>
       <c r="O31">
-        <v>3.62100657</v>
+        <v>3.6087999</v>
       </c>
       <c r="P31">
-        <v>20.51903723</v>
+        <v>20.4498661</v>
       </c>
       <c r="Q31">
-        <v>33.61903723</v>
+        <v>33.5498661</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08939991356243501</v>
+        <v>0.08995341855127931</v>
       </c>
       <c r="T31">
-        <v>0.6001692214116328</v>
+        <v>0.6077884259251102</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.22902196235676</v>
+        <v>10.8547212302782</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07617639298589551</v>
+        <v>0.07611014734246217</v>
       </c>
       <c r="C32">
-        <v>139.4994545224816</v>
+        <v>138.0767807993061</v>
       </c>
       <c r="D32">
-        <v>186.6294545224816</v>
+        <v>186.7777807993061</v>
       </c>
       <c r="E32">
-        <v>-79.57000000000001</v>
+        <v>-77.999</v>
       </c>
       <c r="F32">
-        <v>47.13</v>
+        <v>48.701</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3905,28 +3905,28 @@
         <v>26.5</v>
       </c>
       <c r="M32">
-        <v>2.441334</v>
+        <v>2.5227118</v>
       </c>
       <c r="N32">
-        <v>24.058666</v>
+        <v>23.9772882</v>
       </c>
       <c r="O32">
-        <v>3.6087999</v>
+        <v>3.59659323</v>
       </c>
       <c r="P32">
-        <v>20.4498661</v>
+        <v>20.38069497</v>
       </c>
       <c r="Q32">
-        <v>33.5498661</v>
+        <v>33.48069497</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08995341855127931</v>
+        <v>0.09052296716298866</v>
       </c>
       <c r="T32">
-        <v>0.6077884259251102</v>
+        <v>0.6156284769462248</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.8547212302782</v>
+        <v>10.50456893252729</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07611014734246217</v>
+        <v>0.0760439016990288</v>
       </c>
       <c r="C33">
-        <v>138.0767807993061</v>
+        <v>136.6543430322791</v>
       </c>
       <c r="D33">
-        <v>186.7777807993061</v>
+        <v>186.9263430322791</v>
       </c>
       <c r="E33">
-        <v>-77.999</v>
+        <v>-76.428</v>
       </c>
       <c r="F33">
-        <v>48.701</v>
+        <v>50.272</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3987,28 +3987,28 @@
         <v>26.5</v>
       </c>
       <c r="M33">
-        <v>2.5227118</v>
+        <v>2.6040896</v>
       </c>
       <c r="N33">
-        <v>23.9772882</v>
+        <v>23.8959104</v>
       </c>
       <c r="O33">
-        <v>3.59659323</v>
+        <v>3.58438656</v>
       </c>
       <c r="P33">
-        <v>20.38069497</v>
+        <v>20.31152384</v>
       </c>
       <c r="Q33">
-        <v>33.48069497</v>
+        <v>33.41152384</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09052296716298866</v>
+        <v>0.09110926720445414</v>
       </c>
       <c r="T33">
-        <v>0.6156284769462248</v>
+        <v>0.6236991177032544</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.50456893252729</v>
+        <v>10.17630115338581</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0760439016990288</v>
+        <v>0.07597765605559548</v>
       </c>
       <c r="C34">
-        <v>136.6543430322791</v>
+        <v>135.2321417848843</v>
       </c>
       <c r="D34">
-        <v>186.9263430322791</v>
+        <v>187.0751417848843</v>
       </c>
       <c r="E34">
-        <v>-76.428</v>
+        <v>-74.857</v>
       </c>
       <c r="F34">
-        <v>50.272</v>
+        <v>51.843</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4069,28 +4069,28 @@
         <v>26.5</v>
       </c>
       <c r="M34">
-        <v>2.6040896</v>
+        <v>2.6854674</v>
       </c>
       <c r="N34">
-        <v>23.8959104</v>
+        <v>23.8145326</v>
       </c>
       <c r="O34">
-        <v>3.58438656</v>
+        <v>3.57217989</v>
       </c>
       <c r="P34">
-        <v>20.31152384</v>
+        <v>20.24235271</v>
       </c>
       <c r="Q34">
-        <v>33.41152384</v>
+        <v>33.34235271</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09110926720445414</v>
+        <v>0.09171306873969474</v>
       </c>
       <c r="T34">
-        <v>0.6236991177032544</v>
+        <v>0.6320106731097477</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.17630115338581</v>
+        <v>9.867928391162</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07597765605559548</v>
+        <v>0.07640271041216212</v>
       </c>
       <c r="C35">
-        <v>135.2321417848843</v>
+        <v>132.7104943931805</v>
       </c>
       <c r="D35">
-        <v>187.0751417848843</v>
+        <v>186.1244943931805</v>
       </c>
       <c r="E35">
-        <v>-74.857</v>
+        <v>-73.286</v>
       </c>
       <c r="F35">
-        <v>51.843</v>
+        <v>53.414</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4151,45 +4151,45 @@
         <v>26.5</v>
       </c>
       <c r="M35">
-        <v>2.6854674</v>
+        <v>2.857649</v>
       </c>
       <c r="N35">
-        <v>23.8145326</v>
+        <v>23.642351</v>
       </c>
       <c r="O35">
-        <v>3.57217989</v>
+        <v>3.54635265</v>
       </c>
       <c r="P35">
-        <v>20.24235271</v>
+        <v>20.09599835</v>
       </c>
       <c r="Q35">
-        <v>33.34235271</v>
+        <v>33.19599835</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09171306873969474</v>
+        <v>0.09233516729115475</v>
       </c>
       <c r="T35">
-        <v>0.6320106731097477</v>
+        <v>0.6405740938315893</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.15</v>
       </c>
       <c r="W35">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>9.867928391162</v>
+        <v>9.273357224767633</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07640271041216212</v>
+        <v>0.07635091476872878</v>
       </c>
       <c r="C36">
-        <v>132.7104943931805</v>
+        <v>131.25481971658</v>
       </c>
       <c r="D36">
-        <v>186.1244943931805</v>
+        <v>186.23981971658</v>
       </c>
       <c r="E36">
-        <v>-73.286</v>
+        <v>-71.715</v>
       </c>
       <c r="F36">
-        <v>53.414</v>
+        <v>54.98500000000001</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4233,28 +4233,28 @@
         <v>26.5</v>
       </c>
       <c r="M36">
-        <v>2.857649</v>
+        <v>2.9416975</v>
       </c>
       <c r="N36">
-        <v>23.642351</v>
+        <v>23.5583025</v>
       </c>
       <c r="O36">
-        <v>3.54635265</v>
+        <v>3.533745375</v>
       </c>
       <c r="P36">
-        <v>20.09599835</v>
+        <v>20.024557125</v>
       </c>
       <c r="Q36">
-        <v>33.19599835</v>
+        <v>33.124557125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09233516729115475</v>
+        <v>0.09297640733650583</v>
       </c>
       <c r="T36">
-        <v>0.6405740938315893</v>
+        <v>0.6494010044217953</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.273357224767633</v>
+        <v>9.008404161202842</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07635091476872878</v>
+        <v>0.07629911912529544</v>
       </c>
       <c r="C37">
-        <v>131.25481971658</v>
+        <v>129.7992880429325</v>
       </c>
       <c r="D37">
-        <v>186.23981971658</v>
+        <v>186.3552880429325</v>
       </c>
       <c r="E37">
-        <v>-71.715</v>
+        <v>-70.14400000000001</v>
       </c>
       <c r="F37">
-        <v>54.98500000000001</v>
+        <v>56.556</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4315,28 +4315,28 @@
         <v>26.5</v>
       </c>
       <c r="M37">
-        <v>2.9416975</v>
+        <v>3.025746</v>
       </c>
       <c r="N37">
-        <v>23.5583025</v>
+        <v>23.474254</v>
       </c>
       <c r="O37">
-        <v>3.533745375</v>
+        <v>3.521138099999999</v>
       </c>
       <c r="P37">
-        <v>20.024557125</v>
+        <v>19.9531159</v>
       </c>
       <c r="Q37">
-        <v>33.124557125</v>
+        <v>33.0531159</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09297640733650583</v>
+        <v>0.09363768613327414</v>
       </c>
       <c r="T37">
-        <v>0.6494010044217953</v>
+        <v>0.6585037559679451</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.008404161202842</v>
+        <v>8.75817071228054</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07629911912529544</v>
+        <v>0.07624732348186211</v>
       </c>
       <c r="C38">
-        <v>129.7992880429325</v>
+        <v>128.3438996383874</v>
       </c>
       <c r="D38">
-        <v>186.3552880429325</v>
+        <v>186.4708996383874</v>
       </c>
       <c r="E38">
-        <v>-70.14400000000001</v>
+        <v>-68.57300000000001</v>
       </c>
       <c r="F38">
-        <v>56.556</v>
+        <v>58.127</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4397,28 +4397,28 @@
         <v>26.5</v>
       </c>
       <c r="M38">
-        <v>3.025746</v>
+        <v>3.1097945</v>
       </c>
       <c r="N38">
-        <v>23.474254</v>
+        <v>23.3902055</v>
       </c>
       <c r="O38">
-        <v>3.5211381</v>
+        <v>3.508530825</v>
       </c>
       <c r="P38">
-        <v>19.9531159</v>
+        <v>19.881674675</v>
       </c>
       <c r="Q38">
-        <v>33.0531159</v>
+        <v>32.981674675</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09363768613327414</v>
+        <v>0.09431995790771763</v>
       </c>
       <c r="T38">
-        <v>0.658503755967945</v>
+        <v>0.6678954837536552</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.758170712280542</v>
+        <v>8.52146339573242</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07624732348186211</v>
+        <v>0.07619552783842876</v>
       </c>
       <c r="C39">
-        <v>128.3438996383874</v>
+        <v>126.8886547697554</v>
       </c>
       <c r="D39">
-        <v>186.4708996383874</v>
+        <v>186.5866547697554</v>
       </c>
       <c r="E39">
-        <v>-68.57300000000001</v>
+        <v>-67.00200000000001</v>
       </c>
       <c r="F39">
-        <v>58.127</v>
+        <v>59.698</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4479,28 +4479,28 @@
         <v>26.5</v>
       </c>
       <c r="M39">
-        <v>3.1097945</v>
+        <v>3.193843</v>
       </c>
       <c r="N39">
-        <v>23.3902055</v>
+        <v>23.306157</v>
       </c>
       <c r="O39">
-        <v>3.508530825</v>
+        <v>3.49592355</v>
       </c>
       <c r="P39">
-        <v>19.881674675</v>
+        <v>19.81023345</v>
       </c>
       <c r="Q39">
-        <v>32.981674675</v>
+        <v>32.91023345</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09431995790771763</v>
+        <v>0.09502423844907865</v>
       </c>
       <c r="T39">
-        <v>0.6678954837536552</v>
+        <v>0.6775901705001947</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.52146339573242</v>
+        <v>8.29721435900262</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07619552783842876</v>
+        <v>0.07614373219499541</v>
       </c>
       <c r="C40">
-        <v>126.8886547697554</v>
+        <v>125.4335537045099</v>
       </c>
       <c r="D40">
-        <v>186.5866547697554</v>
+        <v>186.7025537045099</v>
       </c>
       <c r="E40">
-        <v>-67.00200000000001</v>
+        <v>-65.43100000000001</v>
       </c>
       <c r="F40">
-        <v>59.698</v>
+        <v>61.269</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4561,28 +4561,28 @@
         <v>26.5</v>
       </c>
       <c r="M40">
-        <v>3.193843</v>
+        <v>3.2778915</v>
       </c>
       <c r="N40">
-        <v>23.306157</v>
+        <v>23.2221085</v>
       </c>
       <c r="O40">
-        <v>3.49592355</v>
+        <v>3.483316275</v>
       </c>
       <c r="P40">
-        <v>19.81023345</v>
+        <v>19.738792225</v>
       </c>
       <c r="Q40">
-        <v>32.91023345</v>
+        <v>32.838792225</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09502423844907865</v>
+        <v>0.09575161015573019</v>
       </c>
       <c r="T40">
-        <v>0.6775901705001947</v>
+        <v>0.6876027158285879</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.29721435900262</v>
+        <v>8.084465272874347</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07614373219499541</v>
+        <v>0.07609193655156207</v>
       </c>
       <c r="C41">
-        <v>125.4335537045099</v>
+        <v>123.9785967107894</v>
       </c>
       <c r="D41">
-        <v>186.7025537045099</v>
+        <v>186.8185967107894</v>
       </c>
       <c r="E41">
-        <v>-65.43100000000001</v>
+        <v>-63.86</v>
       </c>
       <c r="F41">
-        <v>61.269</v>
+        <v>62.84</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4643,28 +4643,28 @@
         <v>26.5</v>
       </c>
       <c r="M41">
-        <v>3.2778915</v>
+        <v>3.36194</v>
       </c>
       <c r="N41">
-        <v>23.2221085</v>
+        <v>23.13806</v>
       </c>
       <c r="O41">
-        <v>3.483316275</v>
+        <v>3.470709</v>
       </c>
       <c r="P41">
-        <v>19.738792225</v>
+        <v>19.667351</v>
       </c>
       <c r="Q41">
-        <v>32.838792225</v>
+        <v>32.767351</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09575161015573019</v>
+        <v>0.0965032275859368</v>
       </c>
       <c r="T41">
-        <v>0.6876027158285879</v>
+        <v>0.6979490126679276</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.084465272874347</v>
+        <v>7.882353641052487</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07609193655156207</v>
+        <v>0.07604014090812873</v>
       </c>
       <c r="C42">
-        <v>123.9785967107894</v>
+        <v>122.5237840573994</v>
       </c>
       <c r="D42">
-        <v>186.8185967107894</v>
+        <v>186.9347840573994</v>
       </c>
       <c r="E42">
-        <v>-63.86</v>
+        <v>-62.289</v>
       </c>
       <c r="F42">
-        <v>62.84</v>
+        <v>64.411</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4725,28 +4725,28 @@
         <v>26.5</v>
       </c>
       <c r="M42">
-        <v>3.36194</v>
+        <v>3.4459885</v>
       </c>
       <c r="N42">
-        <v>23.13806</v>
+        <v>23.0540115</v>
       </c>
       <c r="O42">
-        <v>3.470709</v>
+        <v>3.458101725</v>
       </c>
       <c r="P42">
-        <v>19.667351</v>
+        <v>19.595909775</v>
       </c>
       <c r="Q42">
-        <v>32.767351</v>
+        <v>32.695909775</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0965032275859368</v>
+        <v>0.09728032357309954</v>
       </c>
       <c r="T42">
-        <v>0.6979490126679276</v>
+        <v>0.7086460314340246</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.882353641052487</v>
+        <v>7.69010111322194</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07604014090812873</v>
+        <v>0.07627394526469539</v>
       </c>
       <c r="C43">
-        <v>122.5237840573994</v>
+        <v>120.429459996327</v>
       </c>
       <c r="D43">
-        <v>186.9347840573994</v>
+        <v>186.411459996327</v>
       </c>
       <c r="E43">
-        <v>-62.289</v>
+        <v>-60.718</v>
       </c>
       <c r="F43">
-        <v>64.411</v>
+        <v>65.982</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4807,45 +4807,45 @@
         <v>26.5</v>
       </c>
       <c r="M43">
-        <v>3.4459885</v>
+        <v>3.5828226</v>
       </c>
       <c r="N43">
-        <v>23.0540115</v>
+        <v>22.9171774</v>
       </c>
       <c r="O43">
-        <v>3.458101725</v>
+        <v>3.43757661</v>
       </c>
       <c r="P43">
-        <v>19.595909775</v>
+        <v>19.47960079</v>
       </c>
       <c r="Q43">
-        <v>32.695909775</v>
+        <v>32.57960079</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09728032357309954</v>
+        <v>0.09808421597361273</v>
       </c>
       <c r="T43">
-        <v>0.7086460314340246</v>
+        <v>0.7197119129161939</v>
       </c>
       <c r="U43">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V43">
         <v>0.15</v>
       </c>
       <c r="W43">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>7.69010111322194</v>
+        <v>7.396403048255864</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07627394526469539</v>
+        <v>0.07622894962126205</v>
       </c>
       <c r="C44">
-        <v>120.429459996327</v>
+        <v>118.9589458907964</v>
       </c>
       <c r="D44">
-        <v>186.411459996327</v>
+        <v>186.5119458907964</v>
       </c>
       <c r="E44">
-        <v>-60.718</v>
+        <v>-59.14700000000001</v>
       </c>
       <c r="F44">
-        <v>65.982</v>
+        <v>67.553</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4889,28 +4889,28 @@
         <v>26.5</v>
       </c>
       <c r="M44">
-        <v>3.5828226</v>
+        <v>3.6681279</v>
       </c>
       <c r="N44">
-        <v>22.9171774</v>
+        <v>22.8318721</v>
       </c>
       <c r="O44">
-        <v>3.43757661</v>
+        <v>3.424780815</v>
       </c>
       <c r="P44">
-        <v>19.47960079</v>
+        <v>19.407091285</v>
       </c>
       <c r="Q44">
-        <v>32.57960079</v>
+        <v>32.507091285</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09808421597361272</v>
+        <v>0.09891631512502112</v>
       </c>
       <c r="T44">
-        <v>0.7197119129161937</v>
+        <v>0.7311660709415971</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.396403048255864</v>
+        <v>7.224393675040611</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07622894962126205</v>
+        <v>0.07618395397782871</v>
       </c>
       <c r="C45">
-        <v>118.9589458907964</v>
+        <v>117.4885401783976</v>
       </c>
       <c r="D45">
-        <v>186.5119458907964</v>
+        <v>186.6125401783976</v>
       </c>
       <c r="E45">
-        <v>-59.14700000000001</v>
+        <v>-57.57600000000001</v>
       </c>
       <c r="F45">
-        <v>67.553</v>
+        <v>69.124</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4971,28 +4971,28 @@
         <v>26.5</v>
       </c>
       <c r="M45">
-        <v>3.6681279</v>
+        <v>3.7534332</v>
       </c>
       <c r="N45">
-        <v>22.8318721</v>
+        <v>22.7465668</v>
       </c>
       <c r="O45">
-        <v>3.424780815</v>
+        <v>3.41198502</v>
       </c>
       <c r="P45">
-        <v>19.407091285</v>
+        <v>19.33458178</v>
       </c>
       <c r="Q45">
-        <v>32.507091285</v>
+        <v>32.43458178</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09891631512502112</v>
+        <v>0.09977813210326553</v>
       </c>
       <c r="T45">
-        <v>0.7311660709415971</v>
+        <v>0.7430293060393363</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.224393675040611</v>
+        <v>7.06020290969878</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07618395397782871</v>
+        <v>0.07613895833439537</v>
       </c>
       <c r="C46">
-        <v>117.4885401783976</v>
+        <v>116.0182430346092</v>
       </c>
       <c r="D46">
-        <v>186.6125401783976</v>
+        <v>186.7132430346091</v>
       </c>
       <c r="E46">
-        <v>-57.57600000000001</v>
+        <v>-56.00500000000001</v>
       </c>
       <c r="F46">
-        <v>69.124</v>
+        <v>70.69499999999999</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5053,28 +5053,28 @@
         <v>26.5</v>
       </c>
       <c r="M46">
-        <v>3.7534332</v>
+        <v>3.8387385</v>
       </c>
       <c r="N46">
-        <v>22.7465668</v>
+        <v>22.6612615</v>
       </c>
       <c r="O46">
-        <v>3.41198502</v>
+        <v>3.399189225</v>
       </c>
       <c r="P46">
-        <v>19.33458178</v>
+        <v>19.262072275</v>
       </c>
       <c r="Q46">
-        <v>32.43458178</v>
+        <v>32.362072275</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09977813210326553</v>
+        <v>0.1006712878807188</v>
       </c>
       <c r="T46">
-        <v>0.7430293060393363</v>
+        <v>0.7553239315042659</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.06020290969878</v>
+        <v>6.903309511705474</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07613895833439537</v>
+        <v>0.07609396269096202</v>
       </c>
       <c r="C47">
-        <v>116.0182430346092</v>
+        <v>114.5480546352886</v>
       </c>
       <c r="D47">
-        <v>186.7132430346091</v>
+        <v>186.8140546352886</v>
       </c>
       <c r="E47">
-        <v>-56.00500000000001</v>
+        <v>-54.434</v>
       </c>
       <c r="F47">
-        <v>70.69499999999999</v>
+        <v>72.26600000000001</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5135,28 +5135,28 @@
         <v>26.5</v>
       </c>
       <c r="M47">
-        <v>3.8387385</v>
+        <v>3.9240438</v>
       </c>
       <c r="N47">
-        <v>22.6612615</v>
+        <v>22.5759562</v>
       </c>
       <c r="O47">
-        <v>3.399189225</v>
+        <v>3.38639343</v>
       </c>
       <c r="P47">
-        <v>19.262072275</v>
+        <v>19.18956277</v>
       </c>
       <c r="Q47">
-        <v>32.362072275</v>
+        <v>32.28956277</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1006712878807188</v>
+        <v>0.1015975235017815</v>
       </c>
       <c r="T47">
-        <v>0.7553239315042659</v>
+        <v>0.7680739134678967</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.903309511705474</v>
+        <v>6.753237565798832</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07609396269096202</v>
+        <v>0.07604896704752867</v>
       </c>
       <c r="C48">
-        <v>114.5480546352886</v>
+        <v>113.0779751566734</v>
       </c>
       <c r="D48">
-        <v>186.8140546352886</v>
+        <v>186.9149751566734</v>
       </c>
       <c r="E48">
-        <v>-54.434</v>
+        <v>-52.863</v>
       </c>
       <c r="F48">
-        <v>72.26600000000001</v>
+        <v>73.837</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5217,28 +5217,28 @@
         <v>26.5</v>
       </c>
       <c r="M48">
-        <v>3.9240438</v>
+        <v>4.009349100000001</v>
       </c>
       <c r="N48">
-        <v>22.5759562</v>
+        <v>22.4906509</v>
       </c>
       <c r="O48">
-        <v>3.38639343</v>
+        <v>3.373597635</v>
       </c>
       <c r="P48">
-        <v>19.18956277</v>
+        <v>19.117053265</v>
       </c>
       <c r="Q48">
-        <v>32.28956277</v>
+        <v>32.217053265</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1015975235017815</v>
+        <v>0.1025587114104314</v>
       </c>
       <c r="T48">
-        <v>0.7680739134678967</v>
+        <v>0.7813050268263814</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.753237565798832</v>
+        <v>6.609551660143537</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07604896704752867</v>
+        <v>0.07600397140409532</v>
       </c>
       <c r="C49">
-        <v>113.0779751566734</v>
+        <v>111.6080047753821</v>
       </c>
       <c r="D49">
-        <v>186.9149751566734</v>
+        <v>187.0160047753821</v>
       </c>
       <c r="E49">
-        <v>-52.863</v>
+        <v>-51.292</v>
       </c>
       <c r="F49">
-        <v>73.837</v>
+        <v>75.408</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5299,28 +5299,28 @@
         <v>26.5</v>
       </c>
       <c r="M49">
-        <v>4.009349100000001</v>
+        <v>4.0946544</v>
       </c>
       <c r="N49">
-        <v>22.4906509</v>
+        <v>22.4053456</v>
       </c>
       <c r="O49">
-        <v>3.373597635</v>
+        <v>3.36080184</v>
       </c>
       <c r="P49">
-        <v>19.117053265</v>
+        <v>19.04454376</v>
       </c>
       <c r="Q49">
-        <v>32.217053265</v>
+        <v>32.14454376</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1025587114104314</v>
+        <v>0.1035568680847987</v>
       </c>
       <c r="T49">
-        <v>0.7813050268263814</v>
+        <v>0.7950450291601924</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.609551660143537</v>
+        <v>6.471852667223881</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07600397140409532</v>
+        <v>0.07595897576066198</v>
       </c>
       <c r="C50">
-        <v>111.6080047753821</v>
+        <v>110.1381436684154</v>
       </c>
       <c r="D50">
-        <v>187.0160047753821</v>
+        <v>187.1171436684154</v>
       </c>
       <c r="E50">
-        <v>-51.292</v>
+        <v>-49.721</v>
       </c>
       <c r="F50">
-        <v>75.408</v>
+        <v>76.979</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5381,28 +5381,28 @@
         <v>26.5</v>
       </c>
       <c r="M50">
-        <v>4.0946544</v>
+        <v>4.1799597</v>
       </c>
       <c r="N50">
-        <v>22.4053456</v>
+        <v>22.3200403</v>
       </c>
       <c r="O50">
-        <v>3.36080184</v>
+        <v>3.348006045</v>
       </c>
       <c r="P50">
-        <v>19.04454376</v>
+        <v>18.972034255</v>
       </c>
       <c r="Q50">
-        <v>32.14454376</v>
+        <v>32.072034255</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1035568680847987</v>
+        <v>0.1045941681581607</v>
       </c>
       <c r="T50">
-        <v>0.7950450291601924</v>
+        <v>0.8093238551149372</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.471852667223881</v>
+        <v>6.339774041362168</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07595897576066198</v>
+        <v>0.07591398011722864</v>
       </c>
       <c r="C51">
-        <v>110.1381436684154</v>
+        <v>108.6683920131569</v>
       </c>
       <c r="D51">
-        <v>187.1171436684154</v>
+        <v>187.2183920131569</v>
       </c>
       <c r="E51">
-        <v>-49.721</v>
+        <v>-48.15000000000001</v>
       </c>
       <c r="F51">
-        <v>76.979</v>
+        <v>78.55</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5463,28 +5463,28 @@
         <v>26.5</v>
       </c>
       <c r="M51">
-        <v>4.1799597</v>
+        <v>4.265265</v>
       </c>
       <c r="N51">
-        <v>22.3200403</v>
+        <v>22.234735</v>
       </c>
       <c r="O51">
-        <v>3.348006045</v>
+        <v>3.33521025</v>
       </c>
       <c r="P51">
-        <v>18.972034255</v>
+        <v>18.89952475</v>
       </c>
       <c r="Q51">
-        <v>32.072034255</v>
+        <v>31.99952475</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1045941681581607</v>
+        <v>0.1056729602344573</v>
       </c>
       <c r="T51">
-        <v>0.8093238551149372</v>
+        <v>0.824173834107872</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.339774041362168</v>
+        <v>6.212978560534926</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07591398011722864</v>
+        <v>0.07630248447379528</v>
       </c>
       <c r="C52">
-        <v>108.6683920131569</v>
+        <v>106.2267813030606</v>
       </c>
       <c r="D52">
-        <v>187.2183920131569</v>
+        <v>186.3477813030606</v>
       </c>
       <c r="E52">
-        <v>-48.15000000000001</v>
+        <v>-46.57900000000001</v>
       </c>
       <c r="F52">
-        <v>78.55</v>
+        <v>80.121</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5545,45 +5545,45 @@
         <v>26.5</v>
       </c>
       <c r="M52">
-        <v>4.265265</v>
+        <v>4.430691299999999</v>
       </c>
       <c r="N52">
-        <v>22.234735</v>
+        <v>22.0693087</v>
       </c>
       <c r="O52">
-        <v>3.33521025</v>
+        <v>3.310396305</v>
       </c>
       <c r="P52">
-        <v>18.89952475</v>
+        <v>18.758912395</v>
       </c>
       <c r="Q52">
-        <v>31.99952475</v>
+        <v>31.858912395</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1056729602344573</v>
+        <v>0.1067957846403985</v>
       </c>
       <c r="T52">
-        <v>0.824173834107872</v>
+        <v>0.8396299346923549</v>
       </c>
       <c r="U52">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V52">
         <v>0.15</v>
       </c>
       <c r="W52">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>6.212978560534926</v>
+        <v>5.981007974985755</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07630248447379528</v>
+        <v>0.07626598883036195</v>
       </c>
       <c r="C53">
-        <v>106.2267813030606</v>
+        <v>104.7372207115164</v>
       </c>
       <c r="D53">
-        <v>186.3477813030606</v>
+        <v>186.4292207115164</v>
       </c>
       <c r="E53">
-        <v>-46.57900000000001</v>
+        <v>-45.00800000000001</v>
       </c>
       <c r="F53">
-        <v>80.121</v>
+        <v>81.69199999999999</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5627,28 +5627,28 @@
         <v>26.5</v>
       </c>
       <c r="M53">
-        <v>4.430691299999999</v>
+        <v>4.5175676</v>
       </c>
       <c r="N53">
-        <v>22.0693087</v>
+        <v>21.9824324</v>
       </c>
       <c r="O53">
-        <v>3.310396305</v>
+        <v>3.29736486</v>
       </c>
       <c r="P53">
-        <v>18.758912395</v>
+        <v>18.68506754</v>
       </c>
       <c r="Q53">
-        <v>31.858912395</v>
+        <v>31.78506754</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1067957846403985</v>
+        <v>0.1079653933965874</v>
       </c>
       <c r="T53">
-        <v>0.8396299346923549</v>
+        <v>0.8557300394678581</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.981007974985755</v>
+        <v>5.865988590851414</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07626598883036195</v>
+        <v>0.07622949318692861</v>
       </c>
       <c r="C54">
-        <v>104.7372207115164</v>
+        <v>103.2477313338822</v>
       </c>
       <c r="D54">
-        <v>186.4292207115164</v>
+        <v>186.5107313338822</v>
       </c>
       <c r="E54">
-        <v>-45.00800000000001</v>
+        <v>-43.437</v>
       </c>
       <c r="F54">
-        <v>81.69199999999999</v>
+        <v>83.26300000000001</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5709,28 +5709,28 @@
         <v>26.5</v>
       </c>
       <c r="M54">
-        <v>4.5175676</v>
+        <v>4.604443900000001</v>
       </c>
       <c r="N54">
-        <v>21.9824324</v>
+        <v>21.8955561</v>
       </c>
       <c r="O54">
-        <v>3.29736486</v>
+        <v>3.284333415</v>
       </c>
       <c r="P54">
-        <v>18.68506754</v>
+        <v>18.611222685</v>
       </c>
       <c r="Q54">
-        <v>31.78506754</v>
+        <v>31.711222685</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1079653933965874</v>
+        <v>0.109184772738146</v>
       </c>
       <c r="T54">
-        <v>0.8557300394678581</v>
+        <v>0.8725152550848719</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.865988590851414</v>
+        <v>5.755309560835348</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07622949318692861</v>
+        <v>0.07619299754349526</v>
       </c>
       <c r="C55">
-        <v>103.2477313338822</v>
+        <v>101.7583132636072</v>
       </c>
       <c r="D55">
-        <v>186.5107313338822</v>
+        <v>186.5923132636073</v>
       </c>
       <c r="E55">
-        <v>-43.437</v>
+        <v>-41.866</v>
       </c>
       <c r="F55">
-        <v>83.26300000000001</v>
+        <v>84.834</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5791,28 +5791,28 @@
         <v>26.5</v>
       </c>
       <c r="M55">
-        <v>4.604443900000001</v>
+        <v>4.691320200000001</v>
       </c>
       <c r="N55">
-        <v>21.8955561</v>
+        <v>21.8086798</v>
       </c>
       <c r="O55">
-        <v>3.284333415</v>
+        <v>3.27130197</v>
       </c>
       <c r="P55">
-        <v>18.611222685</v>
+        <v>18.53737783</v>
       </c>
       <c r="Q55">
-        <v>31.711222685</v>
+        <v>31.63737783</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.109184772738146</v>
+        <v>0.1104571685728158</v>
       </c>
       <c r="T55">
-        <v>0.8725152550848719</v>
+        <v>0.8900302626852342</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.755309560835348</v>
+        <v>5.648729754153212</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07619299754349526</v>
+        <v>0.07615650190006192</v>
       </c>
       <c r="C56">
-        <v>101.7583132636072</v>
+        <v>100.2689665943045</v>
       </c>
       <c r="D56">
-        <v>186.5923132636073</v>
+        <v>186.6739665943045</v>
       </c>
       <c r="E56">
-        <v>-41.866</v>
+        <v>-40.295</v>
       </c>
       <c r="F56">
-        <v>84.834</v>
+        <v>86.405</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5873,28 +5873,28 @@
         <v>26.5</v>
       </c>
       <c r="M56">
-        <v>4.691320200000001</v>
+        <v>4.7781965</v>
       </c>
       <c r="N56">
-        <v>21.8086798</v>
+        <v>21.7218035</v>
       </c>
       <c r="O56">
-        <v>3.27130197</v>
+        <v>3.258270525</v>
       </c>
       <c r="P56">
-        <v>18.53737783</v>
+        <v>18.463532975</v>
       </c>
       <c r="Q56">
-        <v>31.63737783</v>
+        <v>31.563532975</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1104571685728158</v>
+        <v>0.1117861153334709</v>
       </c>
       <c r="T56">
-        <v>0.8900302626852342</v>
+        <v>0.9083237150678349</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.648729754153212</v>
+        <v>5.546025576804972</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07615650190006192</v>
+        <v>0.07612000625662857</v>
       </c>
       <c r="C57">
-        <v>100.2689665943045</v>
+        <v>98.77969141975086</v>
       </c>
       <c r="D57">
-        <v>186.6739665943045</v>
+        <v>186.7556914197509</v>
       </c>
       <c r="E57">
-        <v>-40.295</v>
+        <v>-38.724</v>
       </c>
       <c r="F57">
-        <v>86.405</v>
+        <v>87.976</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5955,28 +5955,28 @@
         <v>26.5</v>
       </c>
       <c r="M57">
-        <v>4.7781965</v>
+        <v>4.8650728</v>
       </c>
       <c r="N57">
-        <v>21.7218035</v>
+        <v>21.6349272</v>
       </c>
       <c r="O57">
-        <v>3.258270525</v>
+        <v>3.24523908</v>
       </c>
       <c r="P57">
-        <v>18.463532975</v>
+        <v>18.38968812</v>
       </c>
       <c r="Q57">
-        <v>31.563532975</v>
+        <v>31.48968812</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1117861153334709</v>
+        <v>0.113175468765065</v>
       </c>
       <c r="T57">
-        <v>0.9083237150678349</v>
+        <v>0.9274486880132811</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.546025576804972</v>
+        <v>5.446989405790598</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07612000625662857</v>
+        <v>0.07608351061319522</v>
       </c>
       <c r="C58">
-        <v>98.77969141975086</v>
+        <v>97.29048783388735</v>
       </c>
       <c r="D58">
-        <v>186.7556914197509</v>
+        <v>186.8374878338874</v>
       </c>
       <c r="E58">
-        <v>-38.724</v>
+        <v>-37.15299999999999</v>
       </c>
       <c r="F58">
-        <v>87.976</v>
+        <v>89.54700000000001</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6037,28 +6037,28 @@
         <v>26.5</v>
       </c>
       <c r="M58">
-        <v>4.8650728</v>
+        <v>4.951949100000001</v>
       </c>
       <c r="N58">
-        <v>21.6349272</v>
+        <v>21.5480509</v>
       </c>
       <c r="O58">
-        <v>3.24523908</v>
+        <v>3.232207635</v>
       </c>
       <c r="P58">
-        <v>18.38968812</v>
+        <v>18.315843265</v>
       </c>
       <c r="Q58">
-        <v>31.48968812</v>
+        <v>31.415843265</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.113175468765065</v>
+        <v>0.1146294432865005</v>
       </c>
       <c r="T58">
-        <v>0.9274486880132811</v>
+        <v>0.9474631945840968</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.446989405790598</v>
+        <v>5.351428188145148</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07608351061319522</v>
+        <v>0.07604701496976189</v>
       </c>
       <c r="C59">
-        <v>97.29048783388735</v>
+        <v>95.80135593081984</v>
       </c>
       <c r="D59">
-        <v>186.8374878338874</v>
+        <v>186.9193559308198</v>
       </c>
       <c r="E59">
-        <v>-37.15299999999999</v>
+        <v>-35.58199999999999</v>
       </c>
       <c r="F59">
-        <v>89.54700000000001</v>
+        <v>91.11800000000001</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6119,28 +6119,28 @@
         <v>26.5</v>
       </c>
       <c r="M59">
-        <v>4.951949100000001</v>
+        <v>5.0388254</v>
       </c>
       <c r="N59">
-        <v>21.5480509</v>
+        <v>21.4611746</v>
       </c>
       <c r="O59">
-        <v>3.232207635</v>
+        <v>3.21917619</v>
       </c>
       <c r="P59">
-        <v>18.315843265</v>
+        <v>18.24199841</v>
       </c>
       <c r="Q59">
-        <v>31.415843265</v>
+        <v>31.34199841</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1146294432865005</v>
+        <v>0.1161526546899093</v>
       </c>
       <c r="T59">
-        <v>0.9474631945840968</v>
+        <v>0.9684307728963799</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.351428188145148</v>
+        <v>5.259162184901267</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07604701496976188</v>
+        <v>0.07601051932632853</v>
       </c>
       <c r="C60">
-        <v>95.80135593081991</v>
+        <v>94.3122958048192</v>
       </c>
       <c r="D60">
-        <v>186.9193559308199</v>
+        <v>187.0012958048192</v>
       </c>
       <c r="E60">
-        <v>-35.58200000000001</v>
+        <v>-34.01100000000001</v>
       </c>
       <c r="F60">
-        <v>91.11799999999999</v>
+        <v>92.68899999999999</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6201,28 +6201,28 @@
         <v>26.5</v>
       </c>
       <c r="M60">
-        <v>5.0388254</v>
+        <v>5.1257017</v>
       </c>
       <c r="N60">
-        <v>21.4611746</v>
+        <v>21.3742983</v>
       </c>
       <c r="O60">
-        <v>3.21917619</v>
+        <v>3.206144745</v>
       </c>
       <c r="P60">
-        <v>18.24199841</v>
+        <v>18.168153555</v>
       </c>
       <c r="Q60">
-        <v>31.34199841</v>
+        <v>31.268153555</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1161526546899092</v>
+        <v>0.1177501690886062</v>
       </c>
       <c r="T60">
-        <v>0.9684307728963797</v>
+        <v>0.9904211599068229</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.259162184901267</v>
+        <v>5.170023842784296</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07601051932632853</v>
+        <v>0.07597402368289519</v>
       </c>
       <c r="C61">
-        <v>94.3122958048192</v>
+        <v>92.82330755032146</v>
       </c>
       <c r="D61">
-        <v>187.0012958048192</v>
+        <v>187.0833075503215</v>
       </c>
       <c r="E61">
-        <v>-34.01100000000001</v>
+        <v>-32.44000000000001</v>
       </c>
       <c r="F61">
-        <v>92.68899999999999</v>
+        <v>94.25999999999999</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6283,28 +6283,28 @@
         <v>26.5</v>
       </c>
       <c r="M61">
-        <v>5.1257017</v>
+        <v>5.212578</v>
       </c>
       <c r="N61">
-        <v>21.3742983</v>
+        <v>21.287422</v>
       </c>
       <c r="O61">
-        <v>3.206144745</v>
+        <v>3.1931133</v>
       </c>
       <c r="P61">
-        <v>18.168153555</v>
+        <v>18.0943087</v>
       </c>
       <c r="Q61">
-        <v>31.268153555</v>
+        <v>31.1943087</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1177501690886062</v>
+        <v>0.119427559207238</v>
       </c>
       <c r="T61">
-        <v>0.9904211599068229</v>
+        <v>1.013511066267788</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.170023842784296</v>
+        <v>5.083856778737891</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07597402368289519</v>
+        <v>0.07593752803946185</v>
       </c>
       <c r="C62">
-        <v>92.82330755032146</v>
+        <v>91.33439126192857</v>
       </c>
       <c r="D62">
-        <v>187.0833075503215</v>
+        <v>187.1653912619286</v>
       </c>
       <c r="E62">
-        <v>-32.44000000000001</v>
+        <v>-30.86900000000001</v>
       </c>
       <c r="F62">
-        <v>94.25999999999999</v>
+        <v>95.83099999999999</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6365,28 +6365,28 @@
         <v>26.5</v>
       </c>
       <c r="M62">
-        <v>5.212578</v>
+        <v>5.2994543</v>
       </c>
       <c r="N62">
-        <v>21.287422</v>
+        <v>21.2005457</v>
       </c>
       <c r="O62">
-        <v>3.1931133</v>
+        <v>3.180081855</v>
       </c>
       <c r="P62">
-        <v>18.0943087</v>
+        <v>18.020463845</v>
       </c>
       <c r="Q62">
-        <v>31.1943087</v>
+        <v>31.120463845</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.119427559207238</v>
+        <v>0.1211909693319535</v>
       </c>
       <c r="T62">
-        <v>1.013511066267788</v>
+        <v>1.037785070390855</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.083856778737891</v>
+        <v>5.000514864332352</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07593752803946185</v>
+        <v>0.07590103239602852</v>
       </c>
       <c r="C63">
-        <v>91.33439126192857</v>
+        <v>89.84554703440857</v>
       </c>
       <c r="D63">
-        <v>187.1653912619286</v>
+        <v>187.2475470344086</v>
       </c>
       <c r="E63">
-        <v>-30.86900000000001</v>
+        <v>-29.298</v>
       </c>
       <c r="F63">
-        <v>95.83099999999999</v>
+        <v>97.402</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6447,28 +6447,28 @@
         <v>26.5</v>
       </c>
       <c r="M63">
-        <v>5.2994543</v>
+        <v>5.3863306</v>
       </c>
       <c r="N63">
-        <v>21.2005457</v>
+        <v>21.1136694</v>
       </c>
       <c r="O63">
-        <v>3.180081855</v>
+        <v>3.16705041</v>
       </c>
       <c r="P63">
-        <v>18.020463845</v>
+        <v>17.94661899</v>
       </c>
       <c r="Q63">
-        <v>31.120463845</v>
+        <v>31.04661899</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1211909693319535</v>
+        <v>0.1230471905158645</v>
       </c>
       <c r="T63">
-        <v>1.037785070390855</v>
+        <v>1.063336653678293</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.000514864332352</v>
+        <v>4.919861398778604</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07590103239602852</v>
+        <v>0.07586453675259516</v>
       </c>
       <c r="C64">
-        <v>89.84554703440857</v>
+        <v>88.35677496269601</v>
       </c>
       <c r="D64">
-        <v>187.2475470344086</v>
+        <v>187.329774962696</v>
       </c>
       <c r="E64">
-        <v>-29.298</v>
+        <v>-27.727</v>
       </c>
       <c r="F64">
-        <v>97.402</v>
+        <v>98.973</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6529,28 +6529,28 @@
         <v>26.5</v>
       </c>
       <c r="M64">
-        <v>5.3863306</v>
+        <v>5.4732069</v>
       </c>
       <c r="N64">
-        <v>21.1136694</v>
+        <v>21.0267931</v>
       </c>
       <c r="O64">
-        <v>3.16705041</v>
+        <v>3.154018965</v>
       </c>
       <c r="P64">
-        <v>17.94661899</v>
+        <v>17.872774135</v>
       </c>
       <c r="Q64">
-        <v>31.04661899</v>
+        <v>30.972774135</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1230471905158645</v>
+        <v>0.1250037479799869</v>
       </c>
       <c r="T64">
-        <v>1.063336653678293</v>
+        <v>1.090269403629917</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.919861398778604</v>
+        <v>4.841768360702753</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07586453675259516</v>
+        <v>0.07582804110916183</v>
       </c>
       <c r="C65">
-        <v>88.35677496269601</v>
+        <v>86.86807514189211</v>
       </c>
       <c r="D65">
-        <v>187.329774962696</v>
+        <v>187.4120751418921</v>
       </c>
       <c r="E65">
-        <v>-27.727</v>
+        <v>-26.15600000000001</v>
       </c>
       <c r="F65">
-        <v>98.973</v>
+        <v>100.544</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6611,28 +6611,28 @@
         <v>26.5</v>
       </c>
       <c r="M65">
-        <v>5.4732069</v>
+        <v>5.5600832</v>
       </c>
       <c r="N65">
-        <v>21.0267931</v>
+        <v>20.9399168</v>
       </c>
       <c r="O65">
-        <v>3.154018965</v>
+        <v>3.14098752</v>
       </c>
       <c r="P65">
-        <v>17.872774135</v>
+        <v>17.79892928</v>
       </c>
       <c r="Q65">
-        <v>30.972774135</v>
+        <v>30.89892928</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1250037479799869</v>
+        <v>0.1270690030810051</v>
       </c>
       <c r="T65">
-        <v>1.090269403629917</v>
+        <v>1.118698417467742</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.841768360702753</v>
+        <v>4.766115730066772</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07582804110916183</v>
+        <v>0.07579154546572849</v>
       </c>
       <c r="C66">
-        <v>86.86807514189211</v>
+        <v>85.37944766726538</v>
       </c>
       <c r="D66">
-        <v>187.4120751418921</v>
+        <v>187.4944476672654</v>
       </c>
       <c r="E66">
-        <v>-26.15600000000001</v>
+        <v>-24.58500000000001</v>
       </c>
       <c r="F66">
-        <v>100.544</v>
+        <v>102.115</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6693,28 +6693,28 @@
         <v>26.5</v>
       </c>
       <c r="M66">
-        <v>5.5600832</v>
+        <v>5.6469595</v>
       </c>
       <c r="N66">
-        <v>20.9399168</v>
+        <v>20.8530405</v>
       </c>
       <c r="O66">
-        <v>3.14098752</v>
+        <v>3.127956075</v>
       </c>
       <c r="P66">
-        <v>17.79892928</v>
+        <v>17.725084425</v>
       </c>
       <c r="Q66">
-        <v>30.89892928</v>
+        <v>30.825084425</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1270690030810051</v>
+        <v>0.1292522727592242</v>
       </c>
       <c r="T66">
-        <v>1.118698417467742</v>
+        <v>1.148751946382015</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.766115730066772</v>
+        <v>4.69279087268113</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07579154546572849</v>
+        <v>0.07575504982229514</v>
       </c>
       <c r="C67">
-        <v>85.37944766726538</v>
+        <v>83.89089263425197</v>
       </c>
       <c r="D67">
-        <v>187.4944476672654</v>
+        <v>187.576892634252</v>
       </c>
       <c r="E67">
-        <v>-24.58500000000001</v>
+        <v>-23.014</v>
       </c>
       <c r="F67">
-        <v>102.115</v>
+        <v>103.686</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6775,28 +6775,28 @@
         <v>26.5</v>
       </c>
       <c r="M67">
-        <v>5.6469595</v>
+        <v>5.7338358</v>
       </c>
       <c r="N67">
-        <v>20.8530405</v>
+        <v>20.7661642</v>
       </c>
       <c r="O67">
-        <v>3.127956075</v>
+        <v>3.11492463</v>
       </c>
       <c r="P67">
-        <v>17.725084425</v>
+        <v>17.65123957</v>
       </c>
       <c r="Q67">
-        <v>30.825084425</v>
+        <v>30.75123957</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1292522727592242</v>
+        <v>0.1315639700655739</v>
       </c>
       <c r="T67">
-        <v>1.148751946382015</v>
+        <v>1.180573329938303</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.69279087268113</v>
+        <v>4.62168798067081</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07575504982229514</v>
+        <v>0.07571855417886178</v>
       </c>
       <c r="C68">
-        <v>83.89089263425197</v>
+        <v>82.40241013845588</v>
       </c>
       <c r="D68">
-        <v>187.576892634252</v>
+        <v>187.6594101384559</v>
       </c>
       <c r="E68">
-        <v>-23.014</v>
+        <v>-21.443</v>
       </c>
       <c r="F68">
-        <v>103.686</v>
+        <v>105.257</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6857,28 +6857,28 @@
         <v>26.5</v>
       </c>
       <c r="M68">
-        <v>5.7338358</v>
+        <v>5.820712100000001</v>
       </c>
       <c r="N68">
-        <v>20.7661642</v>
+        <v>20.6792879</v>
       </c>
       <c r="O68">
-        <v>3.11492463</v>
+        <v>3.101893185</v>
       </c>
       <c r="P68">
-        <v>17.65123957</v>
+        <v>17.577394715</v>
       </c>
       <c r="Q68">
-        <v>30.75123957</v>
+        <v>30.677394715</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1315639700655739</v>
+        <v>0.1340157702389751</v>
       </c>
       <c r="T68">
-        <v>1.180573329938303</v>
+        <v>1.214323282194973</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.62168798067081</v>
+        <v>4.552707563048857</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07571855417886178</v>
+        <v>0.07712705853542845</v>
       </c>
       <c r="C69">
-        <v>82.40241013845588</v>
+        <v>77.69853743276155</v>
       </c>
       <c r="D69">
-        <v>187.6594101384559</v>
+        <v>184.5265374327616</v>
       </c>
       <c r="E69">
-        <v>-21.443</v>
+        <v>-19.872</v>
       </c>
       <c r="F69">
-        <v>105.257</v>
+        <v>106.828</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6939,45 +6939,45 @@
         <v>26.5</v>
       </c>
       <c r="M69">
-        <v>5.820712100000001</v>
+        <v>6.1746584</v>
       </c>
       <c r="N69">
-        <v>20.6792879</v>
+        <v>20.3253416</v>
       </c>
       <c r="O69">
-        <v>3.101893185</v>
+        <v>3.04880124</v>
       </c>
       <c r="P69">
-        <v>17.577394715</v>
+        <v>17.27654036</v>
       </c>
       <c r="Q69">
-        <v>30.677394715</v>
+        <v>30.37654036</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1340157702389751</v>
+        <v>0.1366208079232139</v>
       </c>
       <c r="T69">
-        <v>1.214323282194973</v>
+        <v>1.250182606467684</v>
       </c>
       <c r="U69">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V69">
         <v>0.15</v>
       </c>
       <c r="W69">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.552707563048857</v>
+        <v>4.29173539381547</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07712705853542845</v>
+        <v>0.07711181289199512</v>
       </c>
       <c r="C70">
-        <v>77.69853743276155</v>
+        <v>76.1608875436807</v>
       </c>
       <c r="D70">
-        <v>184.5265374327616</v>
+        <v>184.5598875436807</v>
       </c>
       <c r="E70">
-        <v>-19.872</v>
+        <v>-18.301</v>
       </c>
       <c r="F70">
-        <v>106.828</v>
+        <v>108.399</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7021,28 +7021,28 @@
         <v>26.5</v>
       </c>
       <c r="M70">
-        <v>6.1746584</v>
+        <v>6.265462200000001</v>
       </c>
       <c r="N70">
-        <v>20.3253416</v>
+        <v>20.2345378</v>
       </c>
       <c r="O70">
-        <v>3.04880124</v>
+        <v>3.035180669999999</v>
       </c>
       <c r="P70">
-        <v>17.27654036</v>
+        <v>17.19935713</v>
       </c>
       <c r="Q70">
-        <v>30.37654036</v>
+        <v>30.29935713</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1366208079232139</v>
+        <v>0.1393939125548229</v>
       </c>
       <c r="T70">
-        <v>1.250182606467684</v>
+        <v>1.288355435532184</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.29173539381547</v>
+        <v>4.229536330136984</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07711181289199512</v>
+        <v>0.07709656724856176</v>
       </c>
       <c r="C71">
-        <v>76.1608875436807</v>
+        <v>74.62324971173773</v>
       </c>
       <c r="D71">
-        <v>184.5598875436807</v>
+        <v>184.5932497117377</v>
       </c>
       <c r="E71">
-        <v>-18.301</v>
+        <v>-16.72999999999999</v>
       </c>
       <c r="F71">
-        <v>108.399</v>
+        <v>109.97</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7103,28 +7103,28 @@
         <v>26.5</v>
       </c>
       <c r="M71">
-        <v>6.265462200000001</v>
+        <v>6.356266000000002</v>
       </c>
       <c r="N71">
-        <v>20.2345378</v>
+        <v>20.143734</v>
       </c>
       <c r="O71">
-        <v>3.035180669999999</v>
+        <v>3.0215601</v>
       </c>
       <c r="P71">
-        <v>17.19935713</v>
+        <v>17.1221739</v>
       </c>
       <c r="Q71">
-        <v>30.29935713</v>
+        <v>30.2221739</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1393939125548229</v>
+        <v>0.1423518908285392</v>
       </c>
       <c r="T71">
-        <v>1.288355435532184</v>
+        <v>1.32907311986765</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.229536330136984</v>
+        <v>4.169114382563599</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07709656724856176</v>
+        <v>0.07708132160512843</v>
       </c>
       <c r="C72">
-        <v>74.62324971173773</v>
+        <v>73.08562394347236</v>
       </c>
       <c r="D72">
-        <v>184.5932497117377</v>
+        <v>184.6266239434724</v>
       </c>
       <c r="E72">
-        <v>-16.72999999999999</v>
+        <v>-15.15899999999999</v>
       </c>
       <c r="F72">
-        <v>109.97</v>
+        <v>111.541</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7185,28 +7185,28 @@
         <v>26.5</v>
       </c>
       <c r="M72">
-        <v>6.356266000000002</v>
+        <v>6.447069800000001</v>
       </c>
       <c r="N72">
-        <v>20.143734</v>
+        <v>20.0529302</v>
       </c>
       <c r="O72">
-        <v>3.0215601</v>
+        <v>3.00793953</v>
       </c>
       <c r="P72">
-        <v>17.1221739</v>
+        <v>17.04499067</v>
       </c>
       <c r="Q72">
-        <v>30.2221739</v>
+        <v>30.14499067</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1423518908285392</v>
+        <v>0.1455138676038911</v>
       </c>
       <c r="T72">
-        <v>1.32907311986765</v>
+        <v>1.372598920364182</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.169114382563599</v>
+        <v>4.110394461682422</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07708132160512843</v>
+        <v>0.07706607596169507</v>
       </c>
       <c r="C73">
-        <v>73.08562394347237</v>
+        <v>71.54801024542917</v>
       </c>
       <c r="D73">
-        <v>184.6266239434724</v>
+        <v>184.6600102454292</v>
       </c>
       <c r="E73">
-        <v>-15.15900000000001</v>
+        <v>-13.58800000000001</v>
       </c>
       <c r="F73">
-        <v>111.541</v>
+        <v>113.112</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7267,28 +7267,28 @@
         <v>26.5</v>
       </c>
       <c r="M73">
-        <v>6.4470698</v>
+        <v>6.5378736</v>
       </c>
       <c r="N73">
-        <v>20.0529302</v>
+        <v>19.9621264</v>
       </c>
       <c r="O73">
-        <v>3.00793953</v>
+        <v>2.99431896</v>
       </c>
       <c r="P73">
-        <v>17.04499067</v>
+        <v>16.96780744</v>
       </c>
       <c r="Q73">
-        <v>30.14499067</v>
+        <v>30.06780744</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1455138676038911</v>
+        <v>0.1489016998631967</v>
       </c>
       <c r="T73">
-        <v>1.372598920364182</v>
+        <v>1.419233706610467</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.110394461682422</v>
+        <v>4.053305649714611</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07706607596169507</v>
+        <v>0.07922258031826174</v>
       </c>
       <c r="C74">
-        <v>71.54801024542917</v>
+        <v>65.37145039405235</v>
       </c>
       <c r="D74">
-        <v>184.6600102454292</v>
+        <v>180.0544503940523</v>
       </c>
       <c r="E74">
-        <v>-13.58800000000001</v>
+        <v>-12.01700000000001</v>
       </c>
       <c r="F74">
-        <v>113.112</v>
+        <v>114.683</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7349,45 +7349,45 @@
         <v>26.5</v>
       </c>
       <c r="M74">
-        <v>6.5378736</v>
+        <v>7.0300679</v>
       </c>
       <c r="N74">
-        <v>19.9621264</v>
+        <v>19.4699321</v>
       </c>
       <c r="O74">
-        <v>2.99431896</v>
+        <v>2.920489815</v>
       </c>
       <c r="P74">
-        <v>16.96780744</v>
+        <v>16.549442285</v>
       </c>
       <c r="Q74">
-        <v>30.06780744</v>
+        <v>29.649442285</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1489016998631967</v>
+        <v>0.1525404826602286</v>
       </c>
       <c r="T74">
-        <v>1.419233706610467</v>
+        <v>1.469322921467587</v>
       </c>
       <c r="U74">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V74">
         <v>0.15</v>
       </c>
       <c r="W74">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.053305649714611</v>
+        <v>3.769522624383187</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07922258031826174</v>
+        <v>0.07923708467482839</v>
       </c>
       <c r="C75">
-        <v>65.37145039405235</v>
+        <v>63.77025166140146</v>
       </c>
       <c r="D75">
-        <v>180.0544503940523</v>
+        <v>180.0242516614015</v>
       </c>
       <c r="E75">
-        <v>-12.01700000000001</v>
+        <v>-10.44600000000001</v>
       </c>
       <c r="F75">
-        <v>114.683</v>
+        <v>116.254</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7431,28 +7431,28 @@
         <v>26.5</v>
       </c>
       <c r="M75">
-        <v>7.0300679</v>
+        <v>7.126370199999999</v>
       </c>
       <c r="N75">
-        <v>19.4699321</v>
+        <v>19.3736298</v>
       </c>
       <c r="O75">
-        <v>2.920489815</v>
+        <v>2.90604447</v>
       </c>
       <c r="P75">
-        <v>16.549442285</v>
+        <v>16.46758533</v>
       </c>
       <c r="Q75">
-        <v>29.649442285</v>
+        <v>29.56758533</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1525404826602286</v>
+        <v>0.156459171826263</v>
       </c>
       <c r="T75">
-        <v>1.469322921467587</v>
+        <v>1.523265152852179</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.769522624383187</v>
+        <v>3.71858312945909</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07923708467482839</v>
+        <v>0.07925158903139504</v>
       </c>
       <c r="C76">
-        <v>63.77025166140146</v>
+        <v>62.16906305691481</v>
       </c>
       <c r="D76">
-        <v>180.0242516614015</v>
+        <v>179.9940630569148</v>
       </c>
       <c r="E76">
-        <v>-10.44600000000001</v>
+        <v>-8.875000000000014</v>
       </c>
       <c r="F76">
-        <v>116.254</v>
+        <v>117.825</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7513,28 +7513,28 @@
         <v>26.5</v>
       </c>
       <c r="M76">
-        <v>7.126370199999999</v>
+        <v>7.222672499999999</v>
       </c>
       <c r="N76">
-        <v>19.3736298</v>
+        <v>19.2773275</v>
       </c>
       <c r="O76">
-        <v>2.90604447</v>
+        <v>2.891599125</v>
       </c>
       <c r="P76">
-        <v>16.46758533</v>
+        <v>16.385728375</v>
       </c>
       <c r="Q76">
-        <v>29.56758533</v>
+        <v>29.485728375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.156459171826263</v>
+        <v>0.1606913561255802</v>
       </c>
       <c r="T76">
-        <v>1.523265152852179</v>
+        <v>1.581522762747538</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.71858312945909</v>
+        <v>3.669002021066303</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07925158903139504</v>
+        <v>0.0792660933879617</v>
       </c>
       <c r="C77">
-        <v>62.16906305691481</v>
+        <v>60.56788457549804</v>
       </c>
       <c r="D77">
-        <v>179.9940630569148</v>
+        <v>179.963884575498</v>
       </c>
       <c r="E77">
-        <v>-8.875000000000014</v>
+        <v>-7.304000000000002</v>
       </c>
       <c r="F77">
-        <v>117.825</v>
+        <v>119.396</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7595,28 +7595,28 @@
         <v>26.5</v>
       </c>
       <c r="M77">
-        <v>7.222672499999999</v>
+        <v>7.3189748</v>
       </c>
       <c r="N77">
-        <v>19.2773275</v>
+        <v>19.1810252</v>
       </c>
       <c r="O77">
-        <v>2.891599125</v>
+        <v>2.87715378</v>
       </c>
       <c r="P77">
-        <v>16.385728375</v>
+        <v>16.30387142</v>
       </c>
       <c r="Q77">
-        <v>29.485728375</v>
+        <v>29.40387142</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1606913561255802</v>
+        <v>0.1652762224498404</v>
       </c>
       <c r="T77">
-        <v>1.581522762747538</v>
+        <v>1.64463517346751</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.669002021066303</v>
+        <v>3.620725678683851</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0792660933879617</v>
+        <v>0.07928059774452835</v>
       </c>
       <c r="C78">
-        <v>60.56788457549804</v>
+        <v>58.96671621206023</v>
       </c>
       <c r="D78">
-        <v>179.963884575498</v>
+        <v>179.9337162120602</v>
       </c>
       <c r="E78">
-        <v>-7.304000000000002</v>
+        <v>-5.733000000000004</v>
       </c>
       <c r="F78">
-        <v>119.396</v>
+        <v>120.967</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7677,28 +7677,28 @@
         <v>26.5</v>
       </c>
       <c r="M78">
-        <v>7.3189748</v>
+        <v>7.4152771</v>
       </c>
       <c r="N78">
-        <v>19.1810252</v>
+        <v>19.0847229</v>
       </c>
       <c r="O78">
-        <v>2.87715378</v>
+        <v>2.862708435</v>
       </c>
       <c r="P78">
-        <v>16.30387142</v>
+        <v>16.222014465</v>
       </c>
       <c r="Q78">
-        <v>29.40387142</v>
+        <v>29.322014465</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1652762224498404</v>
+        <v>0.1702597728022972</v>
       </c>
       <c r="T78">
-        <v>1.64463517346751</v>
+        <v>1.713235619902262</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.620725678683851</v>
+        <v>3.573703267272372</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07928059774452835</v>
+        <v>0.079295102101095</v>
       </c>
       <c r="C79">
-        <v>58.96671621206023</v>
+        <v>57.36555796151377</v>
       </c>
       <c r="D79">
-        <v>179.9337162120602</v>
+        <v>179.9035579615138</v>
       </c>
       <c r="E79">
-        <v>-5.733000000000004</v>
+        <v>-4.162000000000006</v>
       </c>
       <c r="F79">
-        <v>120.967</v>
+        <v>122.538</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7759,28 +7759,28 @@
         <v>26.5</v>
       </c>
       <c r="M79">
-        <v>7.4152771</v>
+        <v>7.5115794</v>
       </c>
       <c r="N79">
-        <v>19.0847229</v>
+        <v>18.9884206</v>
       </c>
       <c r="O79">
-        <v>2.862708435</v>
+        <v>2.84826309</v>
       </c>
       <c r="P79">
-        <v>16.222014465</v>
+        <v>16.14015751</v>
       </c>
       <c r="Q79">
-        <v>29.322014465</v>
+        <v>29.24015751</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1702597728022972</v>
+        <v>0.1756963731867955</v>
       </c>
       <c r="T79">
-        <v>1.713235619902262</v>
+        <v>1.788072470558356</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.573703267272372</v>
+        <v>3.527886558717598</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.079295102101095</v>
+        <v>0.08118980645766166</v>
       </c>
       <c r="C80">
-        <v>57.36555796151377</v>
+        <v>51.9400385345108</v>
       </c>
       <c r="D80">
-        <v>179.9035579615138</v>
+        <v>176.0490385345108</v>
       </c>
       <c r="E80">
-        <v>-4.162000000000006</v>
+        <v>-2.591000000000008</v>
       </c>
       <c r="F80">
-        <v>122.538</v>
+        <v>124.109</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7841,45 +7841,45 @@
         <v>26.5</v>
       </c>
       <c r="M80">
-        <v>7.5115794</v>
+        <v>7.955386900000001</v>
       </c>
       <c r="N80">
-        <v>18.9884206</v>
+        <v>18.5446131</v>
       </c>
       <c r="O80">
-        <v>2.84826309</v>
+        <v>2.781691965</v>
       </c>
       <c r="P80">
-        <v>16.14015751</v>
+        <v>15.762921135</v>
       </c>
       <c r="Q80">
-        <v>29.24015751</v>
+        <v>28.862921135</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1756963731867955</v>
+        <v>0.1816507450364842</v>
       </c>
       <c r="T80">
-        <v>1.788072470558356</v>
+        <v>1.870036640324554</v>
       </c>
       <c r="U80">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V80">
         <v>0.15</v>
       </c>
       <c r="W80">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>3.527886558717598</v>
+        <v>3.331076204477245</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08118980645766166</v>
+        <v>0.08122811081422832</v>
       </c>
       <c r="C81">
-        <v>51.9400385345108</v>
+        <v>50.29281610483019</v>
       </c>
       <c r="D81">
-        <v>176.0490385345108</v>
+        <v>175.9728161048302</v>
       </c>
       <c r="E81">
-        <v>-2.591000000000008</v>
+        <v>-1.019999999999996</v>
       </c>
       <c r="F81">
-        <v>124.109</v>
+        <v>125.68</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7923,28 +7923,28 @@
         <v>26.5</v>
       </c>
       <c r="M81">
-        <v>7.955386900000001</v>
+        <v>8.056088000000001</v>
       </c>
       <c r="N81">
-        <v>18.5446131</v>
+        <v>18.443912</v>
       </c>
       <c r="O81">
-        <v>2.781691965</v>
+        <v>2.766586799999999</v>
       </c>
       <c r="P81">
-        <v>15.762921135</v>
+        <v>15.6773252</v>
       </c>
       <c r="Q81">
-        <v>28.862921135</v>
+        <v>28.7773252</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1816507450364842</v>
+        <v>0.1882005540711416</v>
       </c>
       <c r="T81">
-        <v>1.870036640324554</v>
+        <v>1.960197227067371</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.331076204477245</v>
+        <v>3.289437751921279</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08122811081422832</v>
+        <v>0.08126641517079498</v>
       </c>
       <c r="C82">
-        <v>50.29281610483019</v>
+        <v>48.64565964931768</v>
       </c>
       <c r="D82">
-        <v>175.9728161048302</v>
+        <v>175.8966596493177</v>
       </c>
       <c r="E82">
-        <v>-1.019999999999996</v>
+        <v>0.5510000000000019</v>
       </c>
       <c r="F82">
-        <v>125.68</v>
+        <v>127.251</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8005,28 +8005,28 @@
         <v>26.5</v>
       </c>
       <c r="M82">
-        <v>8.056088000000001</v>
+        <v>8.156789100000001</v>
       </c>
       <c r="N82">
-        <v>18.443912</v>
+        <v>18.3432109</v>
       </c>
       <c r="O82">
-        <v>2.766586799999999</v>
+        <v>2.751481635</v>
       </c>
       <c r="P82">
-        <v>15.6773252</v>
+        <v>15.591729265</v>
       </c>
       <c r="Q82">
-        <v>28.7773252</v>
+        <v>28.691729265</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1882005540711416</v>
+        <v>0.1954398166883947</v>
       </c>
       <c r="T82">
-        <v>1.960197227067371</v>
+        <v>2.05984840188838</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.289437751921279</v>
+        <v>3.248827409304968</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08126641517079498</v>
+        <v>0.08130471952736162</v>
       </c>
       <c r="C83">
-        <v>48.64565964931768</v>
+        <v>46.99856908235463</v>
       </c>
       <c r="D83">
-        <v>175.8966596493177</v>
+        <v>175.8205690823546</v>
       </c>
       <c r="E83">
-        <v>0.5510000000000019</v>
+        <v>2.122</v>
       </c>
       <c r="F83">
-        <v>127.251</v>
+        <v>128.822</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8087,28 +8087,28 @@
         <v>26.5</v>
       </c>
       <c r="M83">
-        <v>8.156789100000001</v>
+        <v>8.257490200000001</v>
       </c>
       <c r="N83">
-        <v>18.3432109</v>
+        <v>18.2425098</v>
       </c>
       <c r="O83">
-        <v>2.751481635</v>
+        <v>2.73637647</v>
       </c>
       <c r="P83">
-        <v>15.591729265</v>
+        <v>15.50613333</v>
       </c>
       <c r="Q83">
-        <v>28.691729265</v>
+        <v>28.60613333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1954398166883947</v>
+        <v>0.2034834418186758</v>
       </c>
       <c r="T83">
-        <v>2.05984840188838</v>
+        <v>2.170571929467279</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.248827409304968</v>
+        <v>3.209207562850029</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08130471952736162</v>
+        <v>0.08134302388392829</v>
       </c>
       <c r="C84">
-        <v>46.99856908235463</v>
+        <v>45.35154431847039</v>
       </c>
       <c r="D84">
-        <v>175.8205690823546</v>
+        <v>175.7445443184704</v>
       </c>
       <c r="E84">
-        <v>2.122</v>
+        <v>3.692999999999998</v>
       </c>
       <c r="F84">
-        <v>128.822</v>
+        <v>130.393</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8169,28 +8169,28 @@
         <v>26.5</v>
       </c>
       <c r="M84">
-        <v>8.257490200000001</v>
+        <v>8.358191300000001</v>
       </c>
       <c r="N84">
-        <v>18.2425098</v>
+        <v>18.1418087</v>
       </c>
       <c r="O84">
-        <v>2.73637647</v>
+        <v>2.721271305</v>
       </c>
       <c r="P84">
-        <v>15.50613333</v>
+        <v>15.420537395</v>
       </c>
       <c r="Q84">
-        <v>28.60613333</v>
+        <v>28.520537395</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2034834418186758</v>
+        <v>0.2124733757878136</v>
       </c>
       <c r="T84">
-        <v>2.170571929467279</v>
+        <v>2.294321754408401</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.209207562850029</v>
+        <v>3.17054241149039</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08134302388392829</v>
+        <v>0.08138132824049496</v>
       </c>
       <c r="C85">
-        <v>45.35154431847039</v>
+        <v>43.70458527234226</v>
       </c>
       <c r="D85">
-        <v>175.7445443184704</v>
+        <v>175.6685852723423</v>
       </c>
       <c r="E85">
-        <v>3.692999999999998</v>
+        <v>5.263999999999996</v>
       </c>
       <c r="F85">
-        <v>130.393</v>
+        <v>131.964</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8251,28 +8251,28 @@
         <v>26.5</v>
       </c>
       <c r="M85">
-        <v>8.358191300000001</v>
+        <v>8.4588924</v>
       </c>
       <c r="N85">
-        <v>18.1418087</v>
+        <v>18.0411076</v>
       </c>
       <c r="O85">
-        <v>2.721271305</v>
+        <v>2.70616614</v>
       </c>
       <c r="P85">
-        <v>15.420537395</v>
+        <v>15.33494146</v>
       </c>
       <c r="Q85">
-        <v>28.520537395</v>
+        <v>28.43494146</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2124733757878136</v>
+        <v>0.2225870515030935</v>
       </c>
       <c r="T85">
-        <v>2.294321754408401</v>
+        <v>2.433540307467164</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.17054241149039</v>
+        <v>3.132797858972648</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08138132824049496</v>
+        <v>0.08141963259706161</v>
       </c>
       <c r="C86">
-        <v>43.70458527234226</v>
+        <v>42.05769185879484</v>
       </c>
       <c r="D86">
-        <v>175.6685852723423</v>
+        <v>175.5926918587948</v>
       </c>
       <c r="E86">
-        <v>5.263999999999996</v>
+        <v>6.834999999999994</v>
       </c>
       <c r="F86">
-        <v>131.964</v>
+        <v>133.535</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8333,28 +8333,28 @@
         <v>26.5</v>
       </c>
       <c r="M86">
-        <v>8.4588924</v>
+        <v>8.5595935</v>
       </c>
       <c r="N86">
-        <v>18.0411076</v>
+        <v>17.9404065</v>
       </c>
       <c r="O86">
-        <v>2.70616614</v>
+        <v>2.691060975</v>
       </c>
       <c r="P86">
-        <v>15.33494146</v>
+        <v>15.249345525</v>
       </c>
       <c r="Q86">
-        <v>28.43494146</v>
+        <v>28.349345525</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2225870515030934</v>
+        <v>0.234049217313744</v>
       </c>
       <c r="T86">
-        <v>2.433540307467162</v>
+        <v>2.591321334267093</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.132797858972648</v>
+        <v>3.095941413572969</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08141963259706161</v>
+        <v>0.08145793695362827</v>
       </c>
       <c r="C87">
-        <v>42.05769185879484</v>
+        <v>40.4108639927999</v>
       </c>
       <c r="D87">
-        <v>175.5926918587948</v>
+        <v>175.5168639927999</v>
       </c>
       <c r="E87">
-        <v>6.834999999999994</v>
+        <v>8.405999999999992</v>
       </c>
       <c r="F87">
-        <v>133.535</v>
+        <v>135.106</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8415,28 +8415,28 @@
         <v>26.5</v>
       </c>
       <c r="M87">
-        <v>8.5595935</v>
+        <v>8.6602946</v>
       </c>
       <c r="N87">
-        <v>17.9404065</v>
+        <v>17.8397054</v>
       </c>
       <c r="O87">
-        <v>2.691060975</v>
+        <v>2.67595581</v>
       </c>
       <c r="P87">
-        <v>15.249345525</v>
+        <v>15.16374959</v>
       </c>
       <c r="Q87">
-        <v>28.349345525</v>
+        <v>28.26374959</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.234049217313744</v>
+        <v>0.247148835383059</v>
       </c>
       <c r="T87">
-        <v>2.591321334267093</v>
+        <v>2.771642507752727</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.095941413572969</v>
+        <v>3.059942094810493</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08145793695362827</v>
+        <v>0.08149624131019492</v>
       </c>
       <c r="C88">
-        <v>40.4108639927999</v>
+        <v>38.76410158947601</v>
       </c>
       <c r="D88">
-        <v>175.5168639927999</v>
+        <v>175.441101589476</v>
       </c>
       <c r="E88">
-        <v>8.405999999999992</v>
+        <v>9.97699999999999</v>
       </c>
       <c r="F88">
-        <v>135.106</v>
+        <v>136.677</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8497,28 +8497,28 @@
         <v>26.5</v>
       </c>
       <c r="M88">
-        <v>8.6602946</v>
+        <v>8.7609957</v>
       </c>
       <c r="N88">
-        <v>17.8397054</v>
+        <v>17.7390043</v>
       </c>
       <c r="O88">
-        <v>2.67595581</v>
+        <v>2.660850645</v>
       </c>
       <c r="P88">
-        <v>15.16374959</v>
+        <v>15.078153655</v>
       </c>
       <c r="Q88">
-        <v>28.26374959</v>
+        <v>28.178153655</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.247148835383059</v>
+        <v>0.2622637793091916</v>
       </c>
       <c r="T88">
-        <v>2.771642507752727</v>
+        <v>2.979705400236152</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.059942094810493</v>
+        <v>3.02477034659428</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08149624131019492</v>
+        <v>0.08736894566676157</v>
       </c>
       <c r="C89">
-        <v>38.76410158947601</v>
+        <v>26.303153962295</v>
       </c>
       <c r="D89">
-        <v>175.441101589476</v>
+        <v>164.551153962295</v>
       </c>
       <c r="E89">
-        <v>9.97699999999999</v>
+        <v>11.54799999999999</v>
       </c>
       <c r="F89">
-        <v>136.677</v>
+        <v>138.248</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8579,45 +8579,45 @@
         <v>26.5</v>
       </c>
       <c r="M89">
-        <v>8.7609957</v>
+        <v>9.9400312</v>
       </c>
       <c r="N89">
-        <v>17.7390043</v>
+        <v>16.5599688</v>
       </c>
       <c r="O89">
-        <v>2.660850645</v>
+        <v>2.48399532</v>
       </c>
       <c r="P89">
-        <v>15.078153655</v>
+        <v>14.07597348</v>
       </c>
       <c r="Q89">
-        <v>28.178153655</v>
+        <v>27.17597348</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2622637793091916</v>
+        <v>0.2798978805563465</v>
       </c>
       <c r="T89">
-        <v>2.979705400236152</v>
+        <v>3.222445441466815</v>
       </c>
       <c r="U89">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V89">
         <v>0.15</v>
       </c>
       <c r="W89">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>3.02477034659428</v>
+        <v>2.665987607765255</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08736894566676157</v>
+        <v>0.08747355002332824</v>
       </c>
       <c r="C90">
-        <v>26.303153962295</v>
+        <v>24.55042375900624</v>
       </c>
       <c r="D90">
-        <v>164.551153962295</v>
+        <v>164.3694237590062</v>
       </c>
       <c r="E90">
-        <v>11.54799999999999</v>
+        <v>13.11899999999999</v>
       </c>
       <c r="F90">
-        <v>138.248</v>
+        <v>139.819</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8661,28 +8661,28 @@
         <v>26.5</v>
       </c>
       <c r="M90">
-        <v>9.9400312</v>
+        <v>10.0529861</v>
       </c>
       <c r="N90">
-        <v>16.5599688</v>
+        <v>16.4470139</v>
       </c>
       <c r="O90">
-        <v>2.48399532</v>
+        <v>2.467052085</v>
       </c>
       <c r="P90">
-        <v>14.07597348</v>
+        <v>13.979961815</v>
       </c>
       <c r="Q90">
-        <v>27.17597348</v>
+        <v>27.079961815</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2798978805563465</v>
+        <v>0.3007381820302567</v>
       </c>
       <c r="T90">
-        <v>3.222445441466815</v>
+        <v>3.509320035648507</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.665987607765255</v>
+        <v>2.636032690824073</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08747355002332824</v>
+        <v>0.08757815437989488</v>
       </c>
       <c r="C91">
-        <v>24.55042375900624</v>
+        <v>22.7980945183663</v>
       </c>
       <c r="D91">
-        <v>164.3694237590062</v>
+        <v>164.1880945183663</v>
       </c>
       <c r="E91">
-        <v>13.11899999999999</v>
+        <v>14.68999999999998</v>
       </c>
       <c r="F91">
-        <v>139.819</v>
+        <v>141.39</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8743,28 +8743,28 @@
         <v>26.5</v>
       </c>
       <c r="M91">
-        <v>10.0529861</v>
+        <v>10.165941</v>
       </c>
       <c r="N91">
-        <v>16.4470139</v>
+        <v>16.334059</v>
       </c>
       <c r="O91">
-        <v>2.467052085</v>
+        <v>2.45010885</v>
       </c>
       <c r="P91">
-        <v>13.979961815</v>
+        <v>13.88395015</v>
       </c>
       <c r="Q91">
-        <v>27.079961815</v>
+        <v>26.98395015</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3007381820302567</v>
+        <v>0.325746543798949</v>
       </c>
       <c r="T91">
-        <v>3.509320035648507</v>
+        <v>3.853569548666537</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.636032690824073</v>
+        <v>2.606743438703805</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08757815437989488</v>
+        <v>0.08768275873646154</v>
       </c>
       <c r="C92">
-        <v>22.7980945183663</v>
+        <v>21.04616491483418</v>
       </c>
       <c r="D92">
-        <v>164.1880945183663</v>
+        <v>164.0071649148342</v>
       </c>
       <c r="E92">
-        <v>14.68999999999998</v>
+        <v>16.26100000000001</v>
       </c>
       <c r="F92">
-        <v>141.39</v>
+        <v>142.961</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8825,28 +8825,28 @@
         <v>26.5</v>
       </c>
       <c r="M92">
-        <v>10.165941</v>
+        <v>10.2788959</v>
       </c>
       <c r="N92">
-        <v>16.334059</v>
+        <v>16.2211041</v>
       </c>
       <c r="O92">
-        <v>2.45010885</v>
+        <v>2.433165615</v>
       </c>
       <c r="P92">
-        <v>13.88395015</v>
+        <v>13.787938485</v>
       </c>
       <c r="Q92">
-        <v>26.98395015</v>
+        <v>26.887938485</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.325746543798949</v>
+        <v>0.3563123192940172</v>
       </c>
       <c r="T92">
-        <v>3.853569548666537</v>
+        <v>4.274318953466352</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.606743438703805</v>
+        <v>2.578097906410356</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08768275873646154</v>
+        <v>0.0877873630930282</v>
       </c>
       <c r="C93">
-        <v>21.04616491483418</v>
+        <v>19.29463362870536</v>
       </c>
       <c r="D93">
-        <v>164.0071649148342</v>
+        <v>163.8266336287054</v>
       </c>
       <c r="E93">
-        <v>16.26100000000001</v>
+        <v>17.83200000000001</v>
       </c>
       <c r="F93">
-        <v>142.961</v>
+        <v>144.532</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8907,28 +8907,28 @@
         <v>26.5</v>
       </c>
       <c r="M93">
-        <v>10.2788959</v>
+        <v>10.3918508</v>
       </c>
       <c r="N93">
-        <v>16.2211041</v>
+        <v>16.1081492</v>
       </c>
       <c r="O93">
-        <v>2.433165615</v>
+        <v>2.41622238</v>
       </c>
       <c r="P93">
-        <v>13.787938485</v>
+        <v>13.69192682</v>
       </c>
       <c r="Q93">
-        <v>26.887938485</v>
+        <v>26.79192682</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3563123192940172</v>
+        <v>0.3945195386628527</v>
       </c>
       <c r="T93">
-        <v>4.274318953466352</v>
+        <v>4.800255709466121</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.578097906410356</v>
+        <v>2.550075103079809</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0877873630930282</v>
+        <v>0.08789196744959485</v>
       </c>
       <c r="C94">
-        <v>19.29463362870536</v>
+        <v>17.54349934607956</v>
       </c>
       <c r="D94">
-        <v>163.8266336287054</v>
+        <v>163.6464993460796</v>
       </c>
       <c r="E94">
-        <v>17.83200000000001</v>
+        <v>19.40300000000001</v>
       </c>
       <c r="F94">
-        <v>144.532</v>
+        <v>146.103</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8989,28 +8989,28 @@
         <v>26.5</v>
       </c>
       <c r="M94">
-        <v>10.3918508</v>
+        <v>10.5048057</v>
       </c>
       <c r="N94">
-        <v>16.1081492</v>
+        <v>15.9951943</v>
       </c>
       <c r="O94">
-        <v>2.41622238</v>
+        <v>2.399279145</v>
       </c>
       <c r="P94">
-        <v>13.69192682</v>
+        <v>13.595915155</v>
       </c>
       <c r="Q94">
-        <v>26.79192682</v>
+        <v>26.695915155</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3945195386628527</v>
+        <v>0.4436431064227839</v>
       </c>
       <c r="T94">
-        <v>4.800255709466121</v>
+        <v>5.476460110037253</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.550075103079809</v>
+        <v>2.522654940681101</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08789196744959485</v>
+        <v>0.0911126718061615</v>
       </c>
       <c r="C95">
-        <v>17.54349934607956</v>
+        <v>10.61378798118324</v>
       </c>
       <c r="D95">
-        <v>163.6464993460796</v>
+        <v>158.2877879811832</v>
       </c>
       <c r="E95">
-        <v>19.40300000000001</v>
+        <v>20.974</v>
       </c>
       <c r="F95">
-        <v>146.103</v>
+        <v>147.674</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9071,45 +9071,45 @@
         <v>26.5</v>
       </c>
       <c r="M95">
-        <v>10.5048057</v>
+        <v>11.1936892</v>
       </c>
       <c r="N95">
-        <v>15.9951943</v>
+        <v>15.3063108</v>
       </c>
       <c r="O95">
-        <v>2.399279145</v>
+        <v>2.29594662</v>
       </c>
       <c r="P95">
-        <v>13.595915155</v>
+        <v>13.01036418</v>
       </c>
       <c r="Q95">
-        <v>26.695915155</v>
+        <v>26.11036418</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4436431064227839</v>
+        <v>0.5091411967693589</v>
       </c>
       <c r="T95">
-        <v>5.476460110037253</v>
+        <v>6.378065977465429</v>
       </c>
       <c r="U95">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V95">
         <v>0.15</v>
       </c>
       <c r="W95">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y95">
-        <v>2.522654940681101</v>
+        <v>2.367405376951148</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0911126718061615</v>
+        <v>0.09125042616272817</v>
       </c>
       <c r="C96">
-        <v>10.61378798118324</v>
+        <v>8.821403232485238</v>
       </c>
       <c r="D96">
-        <v>158.2877879811832</v>
+        <v>158.0664032324852</v>
       </c>
       <c r="E96">
-        <v>20.974</v>
+        <v>22.545</v>
       </c>
       <c r="F96">
-        <v>147.674</v>
+        <v>149.245</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9153,28 +9153,28 @@
         <v>26.5</v>
       </c>
       <c r="M96">
-        <v>11.1936892</v>
+        <v>11.312771</v>
       </c>
       <c r="N96">
-        <v>15.3063108</v>
+        <v>15.187229</v>
       </c>
       <c r="O96">
-        <v>2.29594662</v>
+        <v>2.27808435</v>
       </c>
       <c r="P96">
-        <v>13.01036418</v>
+        <v>12.90914465</v>
       </c>
       <c r="Q96">
-        <v>26.11036418</v>
+        <v>26.00914465</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5091411967693589</v>
+        <v>0.6008385232545641</v>
       </c>
       <c r="T96">
-        <v>6.378065977465429</v>
+        <v>7.640314191864878</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.367405376951148</v>
+        <v>2.342485320351662</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09125042616272817</v>
+        <v>0.09138818051929481</v>
       </c>
       <c r="C97">
-        <v>8.821403232485238</v>
+        <v>7.02963688594167</v>
       </c>
       <c r="D97">
-        <v>158.0664032324852</v>
+        <v>157.8456368859417</v>
       </c>
       <c r="E97">
-        <v>22.545</v>
+        <v>24.116</v>
       </c>
       <c r="F97">
-        <v>149.245</v>
+        <v>150.816</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9235,28 +9235,28 @@
         <v>26.5</v>
       </c>
       <c r="M97">
-        <v>11.312771</v>
+        <v>11.4318528</v>
       </c>
       <c r="N97">
-        <v>15.187229</v>
+        <v>15.0681472</v>
       </c>
       <c r="O97">
-        <v>2.27808435</v>
+        <v>2.26022208</v>
       </c>
       <c r="P97">
-        <v>12.90914465</v>
+        <v>12.80792512</v>
       </c>
       <c r="Q97">
-        <v>26.00914465</v>
+        <v>25.90792512</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6008385232545641</v>
+        <v>0.7383845129823717</v>
       </c>
       <c r="T97">
-        <v>7.640314191864878</v>
+        <v>9.533686513464049</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.342485320351662</v>
+        <v>2.318084431597999</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09138818051929483</v>
+        <v>0.09152593487586148</v>
       </c>
       <c r="C98">
-        <v>7.029636885941642</v>
+        <v>5.238486354058182</v>
       </c>
       <c r="D98">
-        <v>157.8456368859416</v>
+        <v>157.6254863540582</v>
       </c>
       <c r="E98">
-        <v>24.116</v>
+        <v>25.687</v>
       </c>
       <c r="F98">
-        <v>150.816</v>
+        <v>152.387</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9317,28 +9317,28 @@
         <v>26.5</v>
       </c>
       <c r="M98">
-        <v>11.4318528</v>
+        <v>11.5509346</v>
       </c>
       <c r="N98">
-        <v>15.0681472</v>
+        <v>14.9490654</v>
       </c>
       <c r="O98">
-        <v>2.26022208</v>
+        <v>2.24235981</v>
       </c>
       <c r="P98">
-        <v>12.80792512</v>
+        <v>12.70670559</v>
       </c>
       <c r="Q98">
-        <v>25.90792512</v>
+        <v>25.80670559</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.73838451298237</v>
+        <v>0.9676278291953818</v>
       </c>
       <c r="T98">
-        <v>9.533686513464025</v>
+        <v>12.68930704946263</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.318084431597999</v>
+        <v>2.294186653952659</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09152593487586148</v>
+        <v>0.09166368923242814</v>
       </c>
       <c r="C99">
-        <v>5.238486354058182</v>
+        <v>3.447949063755686</v>
       </c>
       <c r="D99">
-        <v>157.6254863540582</v>
+        <v>157.4059490637557</v>
       </c>
       <c r="E99">
-        <v>25.687</v>
+        <v>27.258</v>
       </c>
       <c r="F99">
-        <v>152.387</v>
+        <v>153.958</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9399,28 +9399,28 @@
         <v>26.5</v>
       </c>
       <c r="M99">
-        <v>11.5509346</v>
+        <v>11.6700164</v>
       </c>
       <c r="N99">
-        <v>14.9490654</v>
+        <v>14.8299836</v>
       </c>
       <c r="O99">
-        <v>2.24235981</v>
+        <v>2.22449754</v>
       </c>
       <c r="P99">
-        <v>12.70670559</v>
+        <v>12.60548606</v>
       </c>
       <c r="Q99">
-        <v>25.80670559</v>
+        <v>25.70548606</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9676278291953818</v>
+        <v>1.426114461621406</v>
       </c>
       <c r="T99">
-        <v>12.68930704946263</v>
+        <v>19.00054812145984</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.294186653952659</v>
+        <v>2.270776586055183</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09166368923242814</v>
+        <v>0.09180144358899479</v>
       </c>
       <c r="C100">
-        <v>3.447949063755686</v>
+        <v>1.658022456270089</v>
       </c>
       <c r="D100">
-        <v>157.4059490637557</v>
+        <v>157.1870224562701</v>
       </c>
       <c r="E100">
-        <v>27.258</v>
+        <v>28.82899999999999</v>
       </c>
       <c r="F100">
-        <v>153.958</v>
+        <v>155.529</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9481,28 +9481,28 @@
         <v>26.5</v>
       </c>
       <c r="M100">
-        <v>11.6700164</v>
+        <v>11.7890982</v>
       </c>
       <c r="N100">
-        <v>14.8299836</v>
+        <v>14.7109018</v>
       </c>
       <c r="O100">
-        <v>2.22449754</v>
+        <v>2.20663527</v>
       </c>
       <c r="P100">
-        <v>12.60548606</v>
+        <v>12.50426653</v>
       </c>
       <c r="Q100">
-        <v>25.70548606</v>
+        <v>25.60426653</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.426114461621406</v>
+        <v>2.801574358899477</v>
       </c>
       <c r="T100">
-        <v>19.00054812145984</v>
+        <v>37.93427133745148</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.270776586055183</v>
+        <v>2.247839448822302</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09180144358899479</v>
-      </c>
-      <c r="C101">
-        <v>1.658022456270089</v>
-      </c>
-      <c r="D101">
-        <v>157.1870224562701</v>
-      </c>
-      <c r="E101">
-        <v>28.82899999999999</v>
-      </c>
-      <c r="F101">
-        <v>155.529</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>30.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>39.6</v>
-      </c>
-      <c r="K101">
-        <v>13.1</v>
-      </c>
-      <c r="L101">
-        <v>26.5</v>
-      </c>
-      <c r="M101">
-        <v>11.7890982</v>
-      </c>
-      <c r="N101">
-        <v>14.7109018</v>
-      </c>
-      <c r="O101">
-        <v>2.20663527</v>
-      </c>
-      <c r="P101">
-        <v>12.50426653</v>
-      </c>
-      <c r="Q101">
-        <v>25.60426653</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.801574358899477</v>
-      </c>
-      <c r="T101">
-        <v>37.93427133745148</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.06443</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.247839448822302</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
